--- a/Walkathon Nominations 2026_Final.xlsx
+++ b/Walkathon Nominations 2026_Final.xlsx
@@ -1,48 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ericsson-my.sharepoint.com/personal/vijay_anand_ericsson_com/Documents/Madras 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epxxvis/projects/walky/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4035EF42-26DC-4746-9095-D69BB08B4F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B743D15-485E-FC47-803E-873F70C39BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C7CF6F89-D708-AC4D-B373-8419D904A776}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$G$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$H$161</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="814">
   <si>
     <t>Team Name</t>
   </si>
@@ -65,6 +46,15 @@
     <t>Strava Profile Link</t>
   </si>
   <si>
+    <t>Strava ID</t>
+  </si>
+  <si>
+    <t>Matching</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Red Bulls</t>
   </si>
   <si>
@@ -83,6 +73,15 @@
     <t>https://strava.app.link/CQ3HdvpPJ4b</t>
   </si>
   <si>
+    <t>178298909</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Assigned</t>
+  </si>
+  <si>
     <t>egunsxx</t>
   </si>
   <si>
@@ -95,6 +94,9 @@
     <t>https://strava.app.link/k4daj9aQJ4b</t>
   </si>
   <si>
+    <t>160251624</t>
+  </si>
+  <si>
     <t>edishan</t>
   </si>
   <si>
@@ -107,6 +109,15 @@
     <t>https://www.strava.com/athletes/179161411</t>
   </si>
   <si>
+    <t>179161411</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Not Logged In</t>
+  </si>
+  <si>
     <t>EMXXSAK</t>
   </si>
   <si>
@@ -119,6 +130,9 @@
     <t>https://www.strava.com/athletes/178458321</t>
   </si>
   <si>
+    <t>178458321</t>
+  </si>
+  <si>
     <t>eiyyapp</t>
   </si>
   <si>
@@ -143,6 +157,9 @@
     <t>https://strava.app.link/A2G92u4RJ4b</t>
   </si>
   <si>
+    <t>1037578607</t>
+  </si>
+  <si>
     <t>evigjai</t>
   </si>
   <si>
@@ -155,6 +172,9 @@
     <t>https://strava.app.link/bu3bsWUCJ4b</t>
   </si>
   <si>
+    <t>197039192</t>
+  </si>
+  <si>
     <t>zsgixxv</t>
   </si>
   <si>
@@ -179,6 +199,9 @@
     <t>https://strava.app.link/H41TxNARJ4b</t>
   </si>
   <si>
+    <t>154156066</t>
+  </si>
+  <si>
     <t>epxxjos</t>
   </si>
   <si>
@@ -191,6 +214,9 @@
     <t>https://strava.app.link/o4TBBEmRJ4b</t>
   </si>
   <si>
+    <t>149435860</t>
+  </si>
+  <si>
     <t>eulanar</t>
   </si>
   <si>
@@ -203,6 +229,9 @@
     <t>https://www.strava.com/athletes/158225815</t>
   </si>
   <si>
+    <t>158225815</t>
+  </si>
+  <si>
     <t>zvsisiv</t>
   </si>
   <si>
@@ -215,6 +244,9 @@
     <t>https://www.strava.com/athletes/147977677</t>
   </si>
   <si>
+    <t>147977677</t>
+  </si>
+  <si>
     <t>earsind</t>
   </si>
   <si>
@@ -230,6 +262,9 @@
     <t>https://www.strava.com/athletes/77721465</t>
   </si>
   <si>
+    <t>77721465</t>
+  </si>
+  <si>
     <t>enaamkn</t>
   </si>
   <si>
@@ -242,6 +277,9 @@
     <t>https://strava.app.link/u4utnUMRJ4b</t>
   </si>
   <si>
+    <t>179106053</t>
+  </si>
+  <si>
     <t>esxxaki</t>
   </si>
   <si>
@@ -266,6 +304,9 @@
     <t>https://strava.app.link/T4p8hxnSJ4b</t>
   </si>
   <si>
+    <t>96902575</t>
+  </si>
+  <si>
     <t>enidkal</t>
   </si>
   <si>
@@ -278,6 +319,9 @@
     <t>https://www.strava.com/athletes/152512201</t>
   </si>
   <si>
+    <t>152512201</t>
+  </si>
+  <si>
     <t>eaintmr</t>
   </si>
   <si>
@@ -290,6 +334,9 @@
     <t>https://strava.app.link/9siEIkmQJ4b</t>
   </si>
   <si>
+    <t>1141909700</t>
+  </si>
+  <si>
     <t>ebapven</t>
   </si>
   <si>
@@ -302,6 +349,9 @@
     <t>https://strava.app.link/XBZxQTJTJ4b</t>
   </si>
   <si>
+    <t>1226420442</t>
+  </si>
+  <si>
     <t>epatgay</t>
   </si>
   <si>
@@ -314,6 +364,9 @@
     <t>Gayathri Reddy Patlolla: https://strava.app.link/PniXxP0OJ4b</t>
   </si>
   <si>
+    <t>178921098</t>
+  </si>
+  <si>
     <t>Yellow Kings</t>
   </si>
   <si>
@@ -329,6 +382,9 @@
     <t>https://strava.app.link/B673vyDSK4b</t>
   </si>
   <si>
+    <t>2005539695</t>
+  </si>
+  <si>
     <t>emohnav</t>
   </si>
   <si>
@@ -341,6 +397,9 @@
     <t>https://strava.app.link/HwiwxKK4K4b</t>
   </si>
   <si>
+    <t>178561763</t>
+  </si>
+  <si>
     <t>estvwxb</t>
   </si>
   <si>
@@ -365,6 +424,9 @@
     <t>https://strava.app.link/1SwgqS6SJ4b</t>
   </si>
   <si>
+    <t>178958397</t>
+  </si>
+  <si>
     <t>zjuikam</t>
   </si>
   <si>
@@ -377,6 +439,9 @@
     <t>https://strava.app.link/sBYMduzVK4b</t>
   </si>
   <si>
+    <t>477585239</t>
+  </si>
+  <si>
     <t>zmahchi</t>
   </si>
   <si>
@@ -401,6 +466,9 @@
     <t>https://strava.app.link/ZlYmk5f0K4b</t>
   </si>
   <si>
+    <t>540064090</t>
+  </si>
+  <si>
     <t>ejaishe</t>
   </si>
   <si>
@@ -413,6 +481,9 @@
     <t>https://strava.app.link/tl6euRYQJ4b</t>
   </si>
   <si>
+    <t>1070340908</t>
+  </si>
+  <si>
     <t>echanxx</t>
   </si>
   <si>
@@ -425,6 +496,9 @@
     <t>https://strava.app.link/Eodij35ZK4b</t>
   </si>
   <si>
+    <t>148011626</t>
+  </si>
+  <si>
     <t>ehjoevl</t>
   </si>
   <si>
@@ -437,6 +511,9 @@
     <t>https://strava.app.link/tbYGA5IRK4b</t>
   </si>
   <si>
+    <t>179134891</t>
+  </si>
+  <si>
     <t>esyahyn</t>
   </si>
   <si>
@@ -449,6 +526,9 @@
     <t>https://strava.app.link/peFQvVMXJ4b</t>
   </si>
   <si>
+    <t>203745377</t>
+  </si>
+  <si>
     <t>esugman</t>
   </si>
   <si>
@@ -461,6 +541,9 @@
     <t>https://strava.app.link/uPHpQhkUJ4b</t>
   </si>
   <si>
+    <t>179138056</t>
+  </si>
+  <si>
     <t>exxxfat</t>
   </si>
   <si>
@@ -473,6 +556,9 @@
     <t>https://strava.app.link/JY48IRuSK4b</t>
   </si>
   <si>
+    <t>147981259</t>
+  </si>
+  <si>
     <t>esumsey</t>
   </si>
   <si>
@@ -485,6 +571,9 @@
     <t>https://strava.app.link/Pf2z6GhYK4b</t>
   </si>
   <si>
+    <t>152816239</t>
+  </si>
+  <si>
     <t>esakxxs</t>
   </si>
   <si>
@@ -497,6 +586,9 @@
     <t>https://strava.app.link/aa2iKiaTK4b</t>
   </si>
   <si>
+    <t>1384405769</t>
+  </si>
+  <si>
     <t>epursiv</t>
   </si>
   <si>
@@ -509,6 +601,9 @@
     <t>https://strava.app.link/gz1fDEA3K4b</t>
   </si>
   <si>
+    <t>179124247</t>
+  </si>
+  <si>
     <t>esxxmaa</t>
   </si>
   <si>
@@ -521,6 +616,9 @@
     <t>https://strava.app.link/bVA85qL5K4b</t>
   </si>
   <si>
+    <t>901447389</t>
+  </si>
+  <si>
     <t>edemjoe</t>
   </si>
   <si>
@@ -533,6 +631,9 @@
     <t>https://strava.app.link/VxFrNj31K4b</t>
   </si>
   <si>
+    <t>1288043522</t>
+  </si>
+  <si>
     <t>eaxxdha</t>
   </si>
   <si>
@@ -545,6 +646,9 @@
     <t>https://strava.app.link/iBaWNnl6K4b</t>
   </si>
   <si>
+    <t>178453452</t>
+  </si>
+  <si>
     <t>ehepacw</t>
   </si>
   <si>
@@ -557,6 +661,9 @@
     <t>https://strava.app.link/Q5cBGut6K4b</t>
   </si>
   <si>
+    <t>178750010</t>
+  </si>
+  <si>
     <t>Blue Knights</t>
   </si>
   <si>
@@ -572,6 +679,9 @@
     <t>https://strava.app.link/UGzsp2FsJ4b</t>
   </si>
   <si>
+    <t>17729278</t>
+  </si>
+  <si>
     <t>EHUMOSH</t>
   </si>
   <si>
@@ -584,6 +694,9 @@
     <t>https://www.strava.com/athletes/160251787</t>
   </si>
   <si>
+    <t>160251787</t>
+  </si>
+  <si>
     <t>evxxvan</t>
   </si>
   <si>
@@ -596,6 +709,9 @@
     <t>https://strava.app.link/U8t5kPfpJ4b</t>
   </si>
   <si>
+    <t>451870771</t>
+  </si>
+  <si>
     <t>eprisun</t>
   </si>
   <si>
@@ -608,6 +724,9 @@
     <t>https://strava.app.link/5Gd8EsYoJ4b</t>
   </si>
   <si>
+    <t>853690980</t>
+  </si>
+  <si>
     <t>evaivai</t>
   </si>
   <si>
@@ -620,6 +739,9 @@
     <t>https://www.strava.com/athletes/329849094</t>
   </si>
   <si>
+    <t>329849094</t>
+  </si>
+  <si>
     <t>ekshxax</t>
   </si>
   <si>
@@ -632,6 +754,9 @@
     <t>https://strava.app.link/YVu2mTYpJ4b</t>
   </si>
   <si>
+    <t>1378679383</t>
+  </si>
+  <si>
     <t>EKXXARM</t>
   </si>
   <si>
@@ -644,6 +769,9 @@
     <t>https://strava.app.link/8csYmJ3nJ4b</t>
   </si>
   <si>
+    <t>1895409946</t>
+  </si>
+  <si>
     <t>ESTATER</t>
   </si>
   <si>
@@ -656,6 +784,9 @@
     <t>https://strava.app.link/sQXH3oxsJ4b</t>
   </si>
   <si>
+    <t>133674529</t>
+  </si>
+  <si>
     <t>EGXXKHL</t>
   </si>
   <si>
@@ -668,6 +799,9 @@
     <t>https://strava.app.link/rAxtWc5rJ4b</t>
   </si>
   <si>
+    <t>148407994</t>
+  </si>
+  <si>
     <t>EEGOSHA</t>
   </si>
   <si>
@@ -680,6 +814,9 @@
     <t>https://www.strava.com/athletes/178955044</t>
   </si>
   <si>
+    <t>178955044</t>
+  </si>
+  <si>
     <t>EALAGVE</t>
   </si>
   <si>
@@ -692,6 +829,9 @@
     <t>https://strava.app.link/A6ncPBrsJ4b</t>
   </si>
   <si>
+    <t>1889901679</t>
+  </si>
+  <si>
     <t>EBALAJA</t>
   </si>
   <si>
@@ -716,6 +856,9 @@
     <t>https://strava.app.link/zm0KwzXzJ4b</t>
   </si>
   <si>
+    <t>179086580</t>
+  </si>
+  <si>
     <t>ZJILPEN</t>
   </si>
   <si>
@@ -728,6 +871,9 @@
     <t>https://www.strava.com/athletes/178649776</t>
   </si>
   <si>
+    <t>178649776</t>
+  </si>
+  <si>
     <t>EAORUPP</t>
   </si>
   <si>
@@ -740,6 +886,9 @@
     <t>https://strava.app.link/8tlVsUWYJ4b</t>
   </si>
   <si>
+    <t>193218565</t>
+  </si>
+  <si>
     <t>ENATRTH</t>
   </si>
   <si>
@@ -752,6 +901,9 @@
     <t>https://www.strava.com/athletes/789469498</t>
   </si>
   <si>
+    <t>789469498</t>
+  </si>
+  <si>
     <t>ezxxxpa</t>
   </si>
   <si>
@@ -764,6 +916,9 @@
     <t>https://www.strava.com/athletes/178319436</t>
   </si>
   <si>
+    <t>178319436</t>
+  </si>
+  <si>
     <t>EPRAKXX</t>
   </si>
   <si>
@@ -788,6 +943,9 @@
     <t>https://strava.app.link/Y6HD6UYXJ4b</t>
   </si>
   <si>
+    <t>147982359</t>
+  </si>
+  <si>
     <t>EVXZAAE</t>
   </si>
   <si>
@@ -800,6 +958,9 @@
     <t>https://strava.app.link/y4oJlhlLJ4b</t>
   </si>
   <si>
+    <t>573726947</t>
+  </si>
+  <si>
     <t>Green Gladiators</t>
   </si>
   <si>
@@ -815,6 +976,9 @@
     <t>https://strava.app.link/npTCUXtSJ4b</t>
   </si>
   <si>
+    <t>968625931</t>
+  </si>
+  <si>
     <t>emmmccc</t>
   </si>
   <si>
@@ -827,6 +991,9 @@
     <t>https://strava.app.link/ER37vfIZJ4b</t>
   </si>
   <si>
+    <t>145817795</t>
+  </si>
+  <si>
     <t>eaayamn</t>
   </si>
   <si>
@@ -839,6 +1006,9 @@
     <t>https://strava.app.link/pgFqqb6RJ4b</t>
   </si>
   <si>
+    <t>180612920</t>
+  </si>
+  <si>
     <t>evenmxx</t>
   </si>
   <si>
@@ -851,6 +1021,9 @@
     <t>https://strava.app.link/wzcjbU7RJ4b</t>
   </si>
   <si>
+    <t>178457670</t>
+  </si>
+  <si>
     <t>eynjoma</t>
   </si>
   <si>
@@ -863,6 +1036,9 @@
     <t>https://strava.app.link/iRYv9rpSJ4b</t>
   </si>
   <si>
+    <t>178980513</t>
+  </si>
+  <si>
     <t>ekeemar</t>
   </si>
   <si>
@@ -875,6 +1051,9 @@
     <t>https://strava.app.link/ESLEEFw1J4b</t>
   </si>
   <si>
+    <t>179152204</t>
+  </si>
+  <si>
     <t>ezsatsx</t>
   </si>
   <si>
@@ -887,6 +1066,9 @@
     <t>https://strava.app.link/bc12hpI0J4b</t>
   </si>
   <si>
+    <t>148311091</t>
+  </si>
+  <si>
     <t>enatsur</t>
   </si>
   <si>
@@ -899,6 +1081,9 @@
     <t>https://strava.app.link/ZUSOkpeSJ4b</t>
   </si>
   <si>
+    <t>631406953</t>
+  </si>
+  <si>
     <t>eopqstz</t>
   </si>
   <si>
@@ -911,6 +1096,9 @@
     <t>https://strava.app.link/KwyD5go2J4b</t>
   </si>
   <si>
+    <t>1122577861</t>
+  </si>
+  <si>
     <t>elenvas</t>
   </si>
   <si>
@@ -923,6 +1111,9 @@
     <t>https://strava.app.link/ps8Ye3IRJ4b</t>
   </si>
   <si>
+    <t>548973571</t>
+  </si>
+  <si>
     <t>esuguma</t>
   </si>
   <si>
@@ -935,6 +1126,9 @@
     <t>https://strava.app.link/s4D8DvF1J4b</t>
   </si>
   <si>
+    <t>160775734</t>
+  </si>
+  <si>
     <t>ethoreh</t>
   </si>
   <si>
@@ -947,6 +1141,9 @@
     <t>https://strava.app.link/ajb4Uc3SJ4b</t>
   </si>
   <si>
+    <t>179125577</t>
+  </si>
+  <si>
     <t>emoqruk</t>
   </si>
   <si>
@@ -959,6 +1156,9 @@
     <t>https://strava.app.link/qJhzBTyRJ4b</t>
   </si>
   <si>
+    <t>179130447</t>
+  </si>
+  <si>
     <t>eegijko</t>
   </si>
   <si>
@@ -971,6 +1171,9 @@
     <t>https://strava.app.link/aL0N9k7XJ4b</t>
   </si>
   <si>
+    <t>70702945</t>
+  </si>
+  <si>
     <t>earulxx</t>
   </si>
   <si>
@@ -983,6 +1186,9 @@
     <t>https://strava.app.link/S91o5XO1J4b</t>
   </si>
   <si>
+    <t>178290317</t>
+  </si>
+  <si>
     <t>esxxvnt</t>
   </si>
   <si>
@@ -995,6 +1201,9 @@
     <t>https://strava.app.link/X5odvK3RJ4b</t>
   </si>
   <si>
+    <t>146559096</t>
+  </si>
+  <si>
     <t>esensun</t>
   </si>
   <si>
@@ -1007,6 +1216,9 @@
     <t>https://strava.app.link/WvQ0rUcSJ4b</t>
   </si>
   <si>
+    <t>1672794101</t>
+  </si>
+  <si>
     <t>esaokam</t>
   </si>
   <si>
@@ -1019,6 +1231,9 @@
     <t>https://strava.app.link/RT7VKffSJ4b</t>
   </si>
   <si>
+    <t>1942887764</t>
+  </si>
+  <si>
     <t>eshsund</t>
   </si>
   <si>
@@ -1031,6 +1246,9 @@
     <t>https://strava.app.link/BYIPPNK1J4b</t>
   </si>
   <si>
+    <t>185503191</t>
+  </si>
+  <si>
     <t>eanjpol</t>
   </si>
   <si>
@@ -1043,6 +1261,9 @@
     <t>https://strava.app.link/g3Vk9V3RJ4b</t>
   </si>
   <si>
+    <t>1601271012</t>
+  </si>
+  <si>
     <t>Grey Gangsters</t>
   </si>
   <si>
@@ -1058,6 +1279,9 @@
     <t>https://strava.app.link/O1QOeWKDJ4b</t>
   </si>
   <si>
+    <t>178471042</t>
+  </si>
+  <si>
     <t>erankam</t>
   </si>
   <si>
@@ -1070,6 +1294,9 @@
     <t>https://strava.app.link/wxW2qGivJ4b</t>
   </si>
   <si>
+    <t>90486922</t>
+  </si>
+  <si>
     <t>ekgsara</t>
   </si>
   <si>
@@ -1082,6 +1309,9 @@
     <t>https://strava.app.link/8n0joOuCJ4b</t>
   </si>
   <si>
+    <t>148346013</t>
+  </si>
+  <si>
     <t>ehnsbnz</t>
   </si>
   <si>
@@ -1094,6 +1324,9 @@
     <t>https://strava.app.link/uafW2c2oJ4b</t>
   </si>
   <si>
+    <t>1123084069</t>
+  </si>
+  <si>
     <t>eaxxkar</t>
   </si>
   <si>
@@ -1106,6 +1339,9 @@
     <t>https://strava.app.link/QIYLySyvJ4b</t>
   </si>
   <si>
+    <t>147982135</t>
+  </si>
+  <si>
     <t>ekganan</t>
   </si>
   <si>
@@ -1118,6 +1354,9 @@
     <t>https://strava.app.link/tmbnnDmqJ4b</t>
   </si>
   <si>
+    <t>1836127174</t>
+  </si>
+  <si>
     <t>ebbbrrr</t>
   </si>
   <si>
@@ -1130,6 +1369,9 @@
     <t>https://strava.app.link/aaLDVZ3NJ4b</t>
   </si>
   <si>
+    <t>71517326</t>
+  </si>
+  <si>
     <t>eraarxx</t>
   </si>
   <si>
@@ -1142,6 +1384,9 @@
     <t>https://strava.app.link/wTa7ucfVJ4b</t>
   </si>
   <si>
+    <t>125725753</t>
+  </si>
+  <si>
     <t>esrraje</t>
   </si>
   <si>
@@ -1154,6 +1399,9 @@
     <t>https://strava.app.link/tQ9jzmfPJ4b</t>
   </si>
   <si>
+    <t>179128907</t>
+  </si>
+  <si>
     <t>erkrkrk</t>
   </si>
   <si>
@@ -1166,6 +1414,9 @@
     <t>https://strava.app.link/GgGoZT3rJ4b</t>
   </si>
   <si>
+    <t>27018590</t>
+  </si>
+  <si>
     <t>xrajkmu</t>
   </si>
   <si>
@@ -1178,6 +1429,9 @@
     <t>https://strava.app.link/UFxXHsKJJ4b</t>
   </si>
   <si>
+    <t>183565553</t>
+  </si>
+  <si>
     <t>eqtucfh</t>
   </si>
   <si>
@@ -1190,6 +1444,9 @@
     <t>https://strava.app.link/UM21fwJUJ4b</t>
   </si>
   <si>
+    <t>178285162</t>
+  </si>
+  <si>
     <t>ebumsha</t>
   </si>
   <si>
@@ -1202,6 +1459,9 @@
     <t>https://strava.app.link/d2EeQeqqJ4b</t>
   </si>
   <si>
+    <t>808764575</t>
+  </si>
+  <si>
     <t>eedrapv</t>
   </si>
   <si>
@@ -1214,6 +1474,9 @@
     <t>https://strava.app.link/gHWOJNSIJ4b</t>
   </si>
   <si>
+    <t>563302152</t>
+  </si>
+  <si>
     <t>ejansxx</t>
   </si>
   <si>
@@ -1226,6 +1489,9 @@
     <t>https://strava.app.link/4LAr3eFtJ4b</t>
   </si>
   <si>
+    <t>147994644</t>
+  </si>
+  <si>
     <t>eswapls</t>
   </si>
   <si>
@@ -1238,6 +1504,9 @@
     <t>https://strava.app.link/y8Qpa4mIJ4b</t>
   </si>
   <si>
+    <t>178929273</t>
+  </si>
+  <si>
     <t>egbaanl</t>
   </si>
   <si>
@@ -1250,6 +1519,9 @@
     <t>https://strava.app.link/k0f0WmipJ4b</t>
   </si>
   <si>
+    <t>1349991670</t>
+  </si>
+  <si>
     <t>esxrhxs</t>
   </si>
   <si>
@@ -1262,6 +1534,9 @@
     <t>https://strava.app.link/nvdvzNKUJ4b</t>
   </si>
   <si>
+    <t>179144124</t>
+  </si>
+  <si>
     <t>earupkx</t>
   </si>
   <si>
@@ -1274,6 +1549,9 @@
     <t>https://strava.app.link/DjW5XhLCJ4b</t>
   </si>
   <si>
+    <t>178918585</t>
+  </si>
+  <si>
     <t>eglukan</t>
   </si>
   <si>
@@ -1286,6 +1564,9 @@
     <t>https://strava.app.link/WSnIGIyHJ4b</t>
   </si>
   <si>
+    <t>1246709436</t>
+  </si>
+  <si>
     <t>Orange Warriors</t>
   </si>
   <si>
@@ -1301,6 +1582,9 @@
     <t>https://www.strava.com/athletes/148349177</t>
   </si>
   <si>
+    <t>148349177</t>
+  </si>
+  <si>
     <t>ECAHARP</t>
   </si>
   <si>
@@ -1313,6 +1597,9 @@
     <t>https://strava.app.link/ANrNXGqUJ4b</t>
   </si>
   <si>
+    <t>425303394</t>
+  </si>
+  <si>
     <t>ezvinnx</t>
   </si>
   <si>
@@ -1325,6 +1612,9 @@
     <t>https://strava.app.link/TgbrxovVJ4b</t>
   </si>
   <si>
+    <t>178950685</t>
+  </si>
+  <si>
     <t>ewxaabf</t>
   </si>
   <si>
@@ -1337,6 +1627,9 @@
     <t>Kamalakannan Sudhakar | Strava Athlete Profile</t>
   </si>
   <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
     <t>ZMANRAO</t>
   </si>
   <si>
@@ -1349,6 +1642,9 @@
     <t>https://strava.app.link/l7aYkAl4J4b</t>
   </si>
   <si>
+    <t>954941200</t>
+  </si>
+  <si>
     <t>ejknnpu</t>
   </si>
   <si>
@@ -1361,6 +1657,9 @@
     <t>https://www.strava.com/athletes/98412194</t>
   </si>
   <si>
+    <t>98412194</t>
+  </si>
+  <si>
     <t>EMKUAKR</t>
   </si>
   <si>
@@ -1373,6 +1672,9 @@
     <t>https://www.strava.com/athletes/147982647</t>
   </si>
   <si>
+    <t>147982647</t>
+  </si>
+  <si>
     <t>ebxxpar</t>
   </si>
   <si>
@@ -1397,6 +1699,9 @@
     <t>https://www.strava.com/athletes/178615937</t>
   </si>
   <si>
+    <t>178615937</t>
+  </si>
+  <si>
     <t>ehemvxx</t>
   </si>
   <si>
@@ -1409,6 +1714,9 @@
     <t xml:space="preserve">https://strava.app.link/ezjCSrlZJ4b </t>
   </si>
   <si>
+    <t>1038600777</t>
+  </si>
+  <si>
     <t>EBALAPO</t>
   </si>
   <si>
@@ -1421,6 +1729,9 @@
     <t>https://strava.app.link/D8jiciVVJ4b</t>
   </si>
   <si>
+    <t>179087030</t>
+  </si>
+  <si>
     <t xml:space="preserve">EGAJSOW </t>
   </si>
   <si>
@@ -1433,6 +1744,9 @@
     <t>https://strava.app.link/BHf7XGVWJ4b</t>
   </si>
   <si>
+    <t>1705002827</t>
+  </si>
+  <si>
     <t>EKMXLOH</t>
   </si>
   <si>
@@ -1445,6 +1759,9 @@
     <t>https://strava.app.link/DcHQxw10J4b</t>
   </si>
   <si>
+    <t>1736790229</t>
+  </si>
+  <si>
     <t>ELNEGAA</t>
   </si>
   <si>
@@ -1457,6 +1774,9 @@
     <t>https://strava.app.link/hfPVLTi3J4b</t>
   </si>
   <si>
+    <t>1806457820</t>
+  </si>
+  <si>
     <t>EHUSJAS</t>
   </si>
   <si>
@@ -1469,6 +1789,9 @@
     <t>https://strava.app.link/XZ5rXfLZJ4b</t>
   </si>
   <si>
+    <t>121739384</t>
+  </si>
+  <si>
     <t>ESHANPR</t>
   </si>
   <si>
@@ -1481,6 +1804,9 @@
     <t>https://strava.app.link/CB3BLSc0J4b</t>
   </si>
   <si>
+    <t>81045800</t>
+  </si>
+  <si>
     <t>EKALYPR</t>
   </si>
   <si>
@@ -1493,6 +1819,9 @@
     <t>https://strava.app.link/b5yOXfDVJ4b</t>
   </si>
   <si>
+    <t>148173149</t>
+  </si>
+  <si>
     <t>ZSLUEKM</t>
   </si>
   <si>
@@ -1505,6 +1834,9 @@
     <t>https://strava.app.link/0e1y7j0UJ4b</t>
   </si>
   <si>
+    <t>148613873</t>
+  </si>
+  <si>
     <t>ECHITKA</t>
   </si>
   <si>
@@ -1517,6 +1849,9 @@
     <t>https://strava.app.link/vzZY8frZJ4b</t>
   </si>
   <si>
+    <t>52291264</t>
+  </si>
+  <si>
     <t>EMSADAR</t>
   </si>
   <si>
@@ -1529,6 +1864,9 @@
     <t>https://strava.app.link/XGhFxNn2J4b</t>
   </si>
   <si>
+    <t>148099145</t>
+  </si>
+  <si>
     <t>Pink Rangers</t>
   </si>
   <si>
@@ -1544,6 +1882,9 @@
     <t>https://strava.app.link/bx4uwXBYJ4b</t>
   </si>
   <si>
+    <t>148410619</t>
+  </si>
+  <si>
     <t>earigov</t>
   </si>
   <si>
@@ -1556,6 +1897,9 @@
     <t>https://strava.app.link/VbKODpj6J4b</t>
   </si>
   <si>
+    <t>178926085</t>
+  </si>
+  <si>
     <t>easwper</t>
   </si>
   <si>
@@ -1568,6 +1912,9 @@
     <t>https://strava.app.link/m1kyGKi8J4b</t>
   </si>
   <si>
+    <t>161475351</t>
+  </si>
+  <si>
     <t>ebiarpr</t>
   </si>
   <si>
@@ -1580,6 +1927,9 @@
     <t>https://strava.app.link/XOVePg45J4b</t>
   </si>
   <si>
+    <t>178750141</t>
+  </si>
+  <si>
     <t>ehhcasa</t>
   </si>
   <si>
@@ -1592,6 +1942,9 @@
     <t>https://strava.app.link/QnwZd368J4b</t>
   </si>
   <si>
+    <t>179163713</t>
+  </si>
+  <si>
     <t>exdxsah</t>
   </si>
   <si>
@@ -1604,6 +1957,9 @@
     <t>https://strava.app.link/zGktT6t7J4b</t>
   </si>
   <si>
+    <t>178559612</t>
+  </si>
+  <si>
     <t>esabdfg</t>
   </si>
   <si>
@@ -1616,6 +1972,9 @@
     <t>https://strava.app.link/JoaEwVXdK4b</t>
   </si>
   <si>
+    <t>51590077</t>
+  </si>
+  <si>
     <t>egirrxx</t>
   </si>
   <si>
@@ -1628,6 +1987,9 @@
     <t>https://strava.app.link/5ufG4zF4K4b</t>
   </si>
   <si>
+    <t>147981809</t>
+  </si>
+  <si>
     <t>EZBDEFN</t>
   </si>
   <si>
@@ -1640,6 +2002,9 @@
     <t>https://strava.app.link/nETDl8eYJ4b</t>
   </si>
   <si>
+    <t>147981017</t>
+  </si>
+  <si>
     <t>ezrammx</t>
   </si>
   <si>
@@ -1652,6 +2017,9 @@
     <t>https://strava.app.link/6l7Ysn65J4b</t>
   </si>
   <si>
+    <t>179086063</t>
+  </si>
+  <si>
     <t>enanpai</t>
   </si>
   <si>
@@ -1664,6 +2032,9 @@
     <t>https://strava.app.link/PnjizJs7J4b</t>
   </si>
   <si>
+    <t>1303641418</t>
+  </si>
+  <si>
     <t>eaxxpir</t>
   </si>
   <si>
@@ -1676,6 +2047,9 @@
     <t>https://strava.app.link/lCmV9115J4b</t>
   </si>
   <si>
+    <t>147984482</t>
+  </si>
+  <si>
     <t>zxpusxr</t>
   </si>
   <si>
@@ -1688,6 +2062,9 @@
     <t>https://strava.app.link/UzKX3wn9J4b</t>
   </si>
   <si>
+    <t>178122713</t>
+  </si>
+  <si>
     <t>earjrap</t>
   </si>
   <si>
@@ -1709,6 +2086,9 @@
     <t>https://strava.app.link/hQx91O95J4b</t>
   </si>
   <si>
+    <t>1868303263</t>
+  </si>
+  <si>
     <t>ebhamac</t>
   </si>
   <si>
@@ -1721,6 +2101,9 @@
     <t>https://strava.app.link/eG0QoFx8J4b</t>
   </si>
   <si>
+    <t>1886923125</t>
+  </si>
+  <si>
     <t>ekinkhu</t>
   </si>
   <si>
@@ -1733,6 +2116,9 @@
     <t>https://strava.app.link/ND9SuCn9J4b</t>
   </si>
   <si>
+    <t>179172545</t>
+  </si>
+  <si>
     <t>ejnoqse</t>
   </si>
   <si>
@@ -1745,6 +2131,9 @@
     <t>https://strava.app.link/mHg2WEq7J4b</t>
   </si>
   <si>
+    <t>141574150</t>
+  </si>
+  <si>
     <t>ezkxxsi</t>
   </si>
   <si>
@@ -1757,6 +2146,9 @@
     <t>https://strava.app.link/4yamPpd8J4b</t>
   </si>
   <si>
+    <t>735069481</t>
+  </si>
+  <si>
     <t>zvelsub</t>
   </si>
   <si>
@@ -1769,6 +2161,9 @@
     <t>https://strava.app.link/OYROuKl7J4b</t>
   </si>
   <si>
+    <t>180411716</t>
+  </si>
+  <si>
     <t>Purple Pirates</t>
   </si>
   <si>
@@ -1784,6 +2179,9 @@
     <t>https://strava.app.link/BWLTfPa7J4b</t>
   </si>
   <si>
+    <t>178345216</t>
+  </si>
+  <si>
     <t>eniasrg</t>
   </si>
   <si>
@@ -1796,6 +2194,9 @@
     <t>https://strava.app.link/YmVMqAO4K4b</t>
   </si>
   <si>
+    <t>130375409</t>
+  </si>
+  <si>
     <t>esrises</t>
   </si>
   <si>
@@ -1808,6 +2209,9 @@
     <t>https://strava.app.link/Aire5xw4K4b</t>
   </si>
   <si>
+    <t>90435831</t>
+  </si>
+  <si>
     <t>eipnsri</t>
   </si>
   <si>
@@ -1820,6 +2224,9 @@
     <t>https://www.strava.com/athletes/178470904</t>
   </si>
   <si>
+    <t>178470904</t>
+  </si>
+  <si>
     <t>evjiags</t>
   </si>
   <si>
@@ -1832,6 +2239,9 @@
     <t>https://strava.app.link/M5UHEePcK4b</t>
   </si>
   <si>
+    <t>178963694</t>
+  </si>
+  <si>
     <t>esatkon</t>
   </si>
   <si>
@@ -1844,6 +2254,9 @@
     <t>https://strava.app.link/dc2cZ45WK4b</t>
   </si>
   <si>
+    <t>178556046</t>
+  </si>
+  <si>
     <t>elksnsx</t>
   </si>
   <si>
@@ -1856,6 +2269,9 @@
     <t>https://strava.app.link/KPtJM299J4b</t>
   </si>
   <si>
+    <t>147981523</t>
+  </si>
+  <si>
     <t>ehosjos</t>
   </si>
   <si>
@@ -1868,6 +2284,9 @@
     <t>https://strava.app.link/BHq7sZ24K4b</t>
   </si>
   <si>
+    <t>1726824161</t>
+  </si>
+  <si>
     <t>echivln</t>
   </si>
   <si>
@@ -1880,6 +2299,9 @@
     <t>https://strava.app.link/ytV3aPR8K4b</t>
   </si>
   <si>
+    <t>178307932</t>
+  </si>
+  <si>
     <t>ekpnuam</t>
   </si>
   <si>
@@ -1892,6 +2314,9 @@
     <t>https://www.strava.com/athletes/1696396610</t>
   </si>
   <si>
+    <t>1696396610</t>
+  </si>
+  <si>
     <t>ezravax</t>
   </si>
   <si>
@@ -1904,6 +2329,9 @@
     <t>https://strava.app.link/0BzOsfX6K4b</t>
   </si>
   <si>
+    <t>15320490</t>
+  </si>
+  <si>
     <t>erxasix</t>
   </si>
   <si>
@@ -1916,6 +2344,9 @@
     <t>https://strava.app.link/6x0H7I77K4b</t>
   </si>
   <si>
+    <t>1037028731</t>
+  </si>
+  <si>
     <t>eaksmvx</t>
   </si>
   <si>
@@ -1928,6 +2359,9 @@
     <t>https://strava.app.link/rjbWzAQ8K4b</t>
   </si>
   <si>
+    <t>1531870892</t>
+  </si>
+  <si>
     <t>epratpx</t>
   </si>
   <si>
@@ -1940,6 +2374,9 @@
     <t>https://strava.app.link/Da2UWUveK4b</t>
   </si>
   <si>
+    <t>181189222</t>
+  </si>
+  <si>
     <t>eponman</t>
   </si>
   <si>
@@ -1952,6 +2389,9 @@
     <t>https://strava.app.link/AwFFaSQ6K4b</t>
   </si>
   <si>
+    <t>1309721020</t>
+  </si>
+  <si>
     <t>eabxsxh</t>
   </si>
   <si>
@@ -1964,6 +2404,9 @@
     <t>https://strava.app.link/z3WnqVP5K4b</t>
   </si>
   <si>
+    <t>1583269286</t>
+  </si>
+  <si>
     <t>emsxneh</t>
   </si>
   <si>
@@ -1976,6 +2419,9 @@
     <t>https://strava.app.link/OxlDSXQ6K4b</t>
   </si>
   <si>
+    <t>371781906</t>
+  </si>
+  <si>
     <t>emrakla</t>
   </si>
   <si>
@@ -1988,6 +2434,9 @@
     <t>https://strava.app.link/ZP2bcSw4K4b</t>
   </si>
   <si>
+    <t>178730882</t>
+  </si>
+  <si>
     <t>erprsai</t>
   </si>
   <si>
@@ -2000,6 +2449,9 @@
     <t>https://strava.app.link/WOsp7HF4K4b</t>
   </si>
   <si>
+    <t>1458999493</t>
+  </si>
+  <si>
     <t>erjxxad</t>
   </si>
   <si>
@@ -2010,13 +2462,16 @@
   </si>
   <si>
     <t>https://strava.app.link/f6vVDnp4K4b</t>
+  </si>
+  <si>
+    <t>960093313</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2112,9 +2567,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2139,6 +2594,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2473,21 +2929,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C94216C-6603-0645-9AE3-ED401F2BACBF}">
-  <dimension ref="A1:G161"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J161"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.875" style="3"/>
+    <col min="8" max="8" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2509,3874 +2968,5316 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5">
         <v>9884372121</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5">
         <v>7550150156</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>22</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5">
         <v>9600009676</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F5" s="5">
         <v>9688987658</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>34</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F6" s="5">
         <v>9500032125</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="H6" s="10">
+        <v>179130630</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F7" s="5">
         <v>9003074836</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F8" s="5">
         <v>7871185020</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>48</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F9" s="5">
         <v>7010034923</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2042172220</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F10" s="5">
         <v>8940145056</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>57</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F11" s="5">
         <v>9790456774</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F12" s="5">
         <v>9710126011</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>67</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F13" s="5">
         <v>9843548843</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>72</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F14" s="5">
         <v>9884851246</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>78</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F15" s="5">
         <v>9849375566</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F16" s="5">
         <v>9360085088</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>88</v>
+      </c>
+      <c r="H16" s="10">
+        <v>1814695088</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F17" s="5">
         <v>8682071086</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>92</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F18" s="5">
         <v>9289150629</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>97</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F19" s="5">
         <v>9894206972</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>102</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F20" s="5">
         <v>9959345018</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>107</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F21" s="9">
         <v>7680088355</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>112</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="F22" s="9">
         <v>7845400004</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>118</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="F23" s="9">
         <v>9003019683</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F24" s="9">
         <v>9994143428</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>128</v>
+      </c>
+      <c r="H24" s="10">
+        <v>68378052</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="F25" s="9">
         <v>8754495334</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>132</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F26" s="9">
         <v>8056145718</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>137</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="F27" s="9">
         <v>9677013602</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="10">
+        <v>19302770193</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="B28" s="5" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="F28" s="9">
         <v>8121866036</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>146</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="F29" s="9">
         <v>9840880941</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>151</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="F30" s="9">
         <v>9791237891</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>156</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="F31" s="9">
         <v>8056107474</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>161</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="F32" s="9">
         <v>7671997628</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>166</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="F33" s="9">
         <v>9600057748</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>171</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="F34" s="9">
         <v>9361378008</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>176</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="F35" s="9">
         <v>9043537377</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>181</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="F36" s="9">
         <v>6384269234</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>186</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="F37" s="9">
         <v>9840381832</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>191</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F38" s="9">
         <v>7358062498</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>196</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F39" s="9">
         <v>9489551321</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>201</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="F40" s="9">
         <v>9585841458</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>206</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="F41" s="9">
         <v>9217341123</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>211</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="F42" s="9">
         <v>9500057470</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.95" customHeight="1">
+        <v>217</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="F43" s="9">
         <v>9566846096</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>222</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="F44" s="9">
         <v>8667299814</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>227</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="F45" s="9">
         <v>9940106980</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>232</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="F46" s="9">
         <v>9756576113</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>237</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="F47" s="9">
         <v>9342540825</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>242</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="F48" s="9">
         <v>9578305550</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>247</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="F49" s="9">
         <v>9790996252</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>252</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="F50" s="9">
         <v>9942491164</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>257</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="F51" s="9">
         <v>8754476223</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>262</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="F52" s="9">
         <v>9980554546</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>267</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>218</v>
+        <v>271</v>
       </c>
       <c r="F53" s="9">
         <v>9840896543</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>272</v>
+      </c>
+      <c r="H53" s="10">
+        <v>1945067124</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="F54" s="9">
         <v>9790998579</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>276</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="F55" s="9">
         <v>9176268402</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>281</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="F56" s="9">
         <v>9150479447</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>286</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="F57" s="9">
         <v>9790175617</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>291</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="F58" s="9">
         <v>9626863727</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>296</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="F59" s="9">
         <v>9036406418</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>301</v>
+      </c>
+      <c r="H59" s="10">
+        <v>1398565901</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="F60" s="9">
         <v>8754029920</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>305</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="F61" s="9">
         <v>9940138533</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>310</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="F62" s="2">
         <v>8825732515</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>316</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="F63" s="2">
         <v>9600017359</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>321</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="F64" s="2">
         <v>9790837947</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>326</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>265</v>
+        <v>328</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="F65" s="2">
         <v>7845966901</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>331</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="F66" s="2">
         <v>9176706661</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>336</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>273</v>
+        <v>338</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>274</v>
+        <v>339</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>275</v>
+        <v>340</v>
       </c>
       <c r="F67" s="2">
         <v>9962915645</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>341</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>278</v>
+        <v>344</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="F68" s="2">
         <v>9840809251</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>346</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="F69" s="2">
         <v>9740400233</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>351</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="F70" s="2">
         <v>9566680183</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>356</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>289</v>
+        <v>358</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>291</v>
+        <v>360</v>
       </c>
       <c r="F71" s="2">
         <v>9176326102</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>361</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="F72" s="2">
         <v>9790771367</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>366</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>299</v>
+        <v>370</v>
       </c>
       <c r="F73" s="2">
         <v>9652605478</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>371</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>301</v>
+        <v>373</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>303</v>
+        <v>375</v>
       </c>
       <c r="F74" s="2">
         <v>9962479899</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>376</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>305</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>306</v>
+        <v>379</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>307</v>
+        <v>380</v>
       </c>
       <c r="F75" s="2">
         <v>9840953018</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>381</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>310</v>
+        <v>384</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="F76" s="2">
         <v>9940076367</v>
       </c>
       <c r="G76" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="B77" s="2" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>314</v>
+        <v>389</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>315</v>
+        <v>390</v>
       </c>
       <c r="F77" s="2">
         <v>8754424332</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>391</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>317</v>
+        <v>393</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>318</v>
+        <v>394</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>319</v>
+        <v>395</v>
       </c>
       <c r="F78" s="2">
         <v>9600071450</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>396</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>321</v>
+        <v>398</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>322</v>
+        <v>399</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>323</v>
+        <v>400</v>
       </c>
       <c r="F79" s="2">
         <v>9742464276</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>401</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>325</v>
+        <v>403</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>326</v>
+        <v>404</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>327</v>
+        <v>405</v>
       </c>
       <c r="F80" s="2">
         <v>9791013221</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>406</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>329</v>
+        <v>408</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>330</v>
+        <v>409</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
       <c r="F81" s="2">
         <v>9115645999</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>411</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>334</v>
+        <v>414</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="F82" s="2">
         <v>9840795835</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>417</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>340</v>
+        <v>421</v>
       </c>
       <c r="F83" s="2">
         <v>9940634523</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>422</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>343</v>
+        <v>425</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="F84" s="2">
         <v>9810792177</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>427</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>346</v>
+        <v>429</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>347</v>
+        <v>430</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>348</v>
+        <v>431</v>
       </c>
       <c r="F85" s="2">
         <v>9176404339</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>432</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>352</v>
+        <v>436</v>
       </c>
       <c r="F86" s="2">
         <v>9176963320</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>437</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="I86" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>354</v>
+        <v>439</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>355</v>
+        <v>440</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="F87" s="2">
         <v>9842501177</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>442</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>358</v>
+        <v>444</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>359</v>
+        <v>445</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="F88" s="2">
         <v>9940653261</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>447</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>362</v>
+        <v>449</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>363</v>
+        <v>450</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>364</v>
+        <v>451</v>
       </c>
       <c r="F89" s="2">
         <v>9962002980</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>452</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>366</v>
+        <v>454</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>368</v>
+        <v>456</v>
       </c>
       <c r="F90" s="2">
         <v>9677014580</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>457</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>370</v>
+        <v>459</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="F91" s="2">
         <v>9500065758</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>462</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>374</v>
+        <v>464</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>375</v>
+        <v>465</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="F92" s="2">
         <v>9962034156</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>467</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J92" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>378</v>
+        <v>469</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>379</v>
+        <v>470</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="F93" s="2">
         <v>9840602620</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>472</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="I93" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>383</v>
+        <v>475</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>384</v>
+        <v>476</v>
       </c>
       <c r="F94" s="2">
         <v>7013568493</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>477</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J94" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>386</v>
+        <v>479</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>388</v>
+        <v>481</v>
       </c>
       <c r="F95" s="2">
         <v>9391299600</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>482</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>390</v>
+        <v>484</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>392</v>
+        <v>486</v>
       </c>
       <c r="F96" s="2">
         <v>9566132657</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>487</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>394</v>
+        <v>489</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>395</v>
+        <v>490</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>396</v>
+        <v>491</v>
       </c>
       <c r="F97" s="2">
         <v>9962190291</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>492</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>398</v>
+        <v>494</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>399</v>
+        <v>495</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>400</v>
+        <v>496</v>
       </c>
       <c r="F98" s="2">
         <v>7200707770</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>497</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>402</v>
+        <v>499</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>404</v>
+        <v>501</v>
       </c>
       <c r="F99" s="2">
         <v>9087992497</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>502</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>406</v>
+        <v>504</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>407</v>
+        <v>505</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>408</v>
+        <v>506</v>
       </c>
       <c r="F100" s="2">
         <v>9487867032</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>507</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J100" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>410</v>
+        <v>509</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>411</v>
+        <v>510</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>412</v>
+        <v>511</v>
       </c>
       <c r="F101" s="2">
         <v>9182233877</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>512</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>415</v>
+        <v>515</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>416</v>
+        <v>516</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>417</v>
+        <v>517</v>
       </c>
       <c r="F102" s="2">
         <v>918197472411</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>518</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>420</v>
+        <v>521</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>421</v>
+        <v>522</v>
       </c>
       <c r="F103" s="2">
         <v>7305914980</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>523</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>423</v>
+        <v>525</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>424</v>
+        <v>526</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>425</v>
+        <v>527</v>
       </c>
       <c r="F104" s="2">
         <v>9566152090</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>528</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>427</v>
+        <v>530</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>428</v>
+        <v>531</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>429</v>
+        <v>532</v>
       </c>
       <c r="F105" s="2">
         <v>8056160260</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>533</v>
+      </c>
+      <c r="H105" s="10">
+        <v>150685394</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>431</v>
+        <v>535</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>432</v>
+        <v>536</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>433</v>
+        <v>537</v>
       </c>
       <c r="F106" s="2">
         <v>9985541711</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>538</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>435</v>
+        <v>540</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>436</v>
+        <v>541</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>437</v>
+        <v>542</v>
       </c>
       <c r="F107" s="2">
         <v>919841248577</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>543</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>439</v>
+        <v>545</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>440</v>
+        <v>546</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>441</v>
+        <v>547</v>
       </c>
       <c r="F108" s="2">
         <v>919500074227</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>548</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>443</v>
+        <v>550</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>444</v>
+        <v>551</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>445</v>
+        <v>552</v>
       </c>
       <c r="F109" s="2">
         <v>6382811325</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>553</v>
+      </c>
+      <c r="H109" s="10">
+        <v>1570233933</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J109" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>447</v>
+        <v>554</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>448</v>
+        <v>555</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>449</v>
+        <v>556</v>
       </c>
       <c r="F110" s="2">
         <v>919600199456</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>557</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>451</v>
+        <v>559</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>452</v>
+        <v>560</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>453</v>
+        <v>561</v>
       </c>
       <c r="F111" s="2">
         <v>918939833531</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>562</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>455</v>
+        <v>564</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>456</v>
+        <v>565</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>457</v>
+        <v>566</v>
       </c>
       <c r="F112" s="2">
         <v>9958777360</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>567</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>459</v>
+        <v>569</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>460</v>
+        <v>570</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>461</v>
+        <v>571</v>
       </c>
       <c r="F113" s="2">
         <v>9894916995</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>572</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J113" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>464</v>
+        <v>575</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>465</v>
+        <v>576</v>
       </c>
       <c r="F114" s="2">
         <v>9500043735</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>577</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>467</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>468</v>
+        <v>580</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>469</v>
+        <v>581</v>
       </c>
       <c r="F115" s="2">
         <v>6369326376</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>582</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J115" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>471</v>
+        <v>584</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>472</v>
+        <v>585</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>473</v>
+        <v>586</v>
       </c>
       <c r="F116" s="2">
         <v>9003724569</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>587</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>475</v>
+        <v>589</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>476</v>
+        <v>590</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>477</v>
+        <v>591</v>
       </c>
       <c r="F117" s="2">
         <v>9894540684</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>592</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>479</v>
+        <v>594</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>480</v>
+        <v>595</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>481</v>
+        <v>596</v>
       </c>
       <c r="F118" s="2">
         <v>9789810530</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>597</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>483</v>
+        <v>599</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>484</v>
+        <v>600</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>485</v>
+        <v>601</v>
       </c>
       <c r="F119" s="2">
         <v>9551635956</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>602</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>487</v>
+        <v>604</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>488</v>
+        <v>605</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>489</v>
+        <v>606</v>
       </c>
       <c r="F120" s="2">
         <v>919884025540</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>607</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="I120" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>491</v>
+        <v>609</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>492</v>
+        <v>610</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>493</v>
+        <v>611</v>
       </c>
       <c r="F121" s="2">
         <v>919677333273</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>612</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="I121" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>496</v>
+        <v>615</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>497</v>
+        <v>616</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>498</v>
+        <v>617</v>
       </c>
       <c r="F122" s="2">
         <v>8754129067</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>618</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="I122" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>500</v>
+        <v>620</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>501</v>
+        <v>621</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>502</v>
+        <v>622</v>
       </c>
       <c r="F123" s="2">
         <v>8144368800</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>623</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I123" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>504</v>
+        <v>625</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>505</v>
+        <v>626</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>506</v>
+        <v>627</v>
       </c>
       <c r="F124" s="2">
         <v>9842756727</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>628</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="I124" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>508</v>
+        <v>630</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>509</v>
+        <v>631</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>510</v>
+        <v>632</v>
       </c>
       <c r="F125" s="2">
         <v>9488833626</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>633</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="I125" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>512</v>
+        <v>635</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>513</v>
+        <v>636</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>514</v>
+        <v>637</v>
       </c>
       <c r="F126" s="2">
         <v>7382432136</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>638</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>516</v>
+        <v>640</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>517</v>
+        <v>641</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>518</v>
+        <v>642</v>
       </c>
       <c r="F127" s="2">
         <v>9842956552</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>643</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="I127" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>520</v>
+        <v>645</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>521</v>
+        <v>646</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>522</v>
+        <v>647</v>
       </c>
       <c r="F128" s="2">
         <v>9790998583</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>648</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="I128" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>524</v>
+        <v>650</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>525</v>
+        <v>651</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>526</v>
+        <v>652</v>
       </c>
       <c r="F129" s="2">
         <v>9123521909</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>653</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="I129" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>528</v>
+        <v>655</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>529</v>
+        <v>656</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>530</v>
+        <v>657</v>
       </c>
       <c r="F130" s="2">
         <v>9790909930</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>658</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>532</v>
+        <v>660</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>533</v>
+        <v>661</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>534</v>
+        <v>662</v>
       </c>
       <c r="F131" s="2">
         <v>9843451933</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>663</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>536</v>
+        <v>665</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>537</v>
+        <v>666</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>538</v>
+        <v>667</v>
       </c>
       <c r="F132" s="2">
         <v>9940182025</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>668</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>540</v>
+        <v>670</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>541</v>
+        <v>671</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>542</v>
+        <v>672</v>
       </c>
       <c r="F133" s="2">
         <v>9092487649</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>673</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="I133" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>544</v>
+        <v>675</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>545</v>
+        <v>676</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>546</v>
+        <v>677</v>
       </c>
       <c r="F134" s="2">
         <v>9900487944</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>678</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="I134" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>548</v>
+        <v>680</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>549</v>
+        <v>681</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>550</v>
+        <v>682</v>
       </c>
       <c r="F135" s="2">
         <v>9751234404</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>623</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I135" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>551</v>
+        <v>683</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>552</v>
+        <v>684</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>553</v>
+        <v>685</v>
       </c>
       <c r="F136" s="2">
         <v>9944194100</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>686</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>555</v>
+        <v>688</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>556</v>
+        <v>689</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>557</v>
+        <v>690</v>
       </c>
       <c r="F137" s="2">
         <v>6361759520</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>691</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="I137" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>559</v>
+        <v>693</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>560</v>
+        <v>694</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>561</v>
+        <v>695</v>
       </c>
       <c r="F138" s="2">
         <v>8376014306</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>696</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="I138" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>563</v>
+        <v>698</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>564</v>
+        <v>699</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>565</v>
+        <v>700</v>
       </c>
       <c r="F139" s="2">
         <v>9790766914</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>701</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="I139" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>567</v>
+        <v>703</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>568</v>
+        <v>704</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>569</v>
+        <v>705</v>
       </c>
       <c r="F140" s="2">
         <v>9841255581</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>706</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="I140" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>571</v>
+        <v>708</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>572</v>
+        <v>709</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>573</v>
+        <v>710</v>
       </c>
       <c r="F141" s="2">
         <v>9843451933</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>711</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="I141" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>576</v>
+        <v>714</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>577</v>
+        <v>715</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>578</v>
+        <v>716</v>
       </c>
       <c r="F142" s="2">
         <v>8754425672</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>717</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="I142" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>580</v>
+        <v>719</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>581</v>
+        <v>720</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>582</v>
+        <v>721</v>
       </c>
       <c r="F143" s="2">
         <v>7397271607</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>722</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="I143" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>584</v>
+        <v>724</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>585</v>
+        <v>725</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>586</v>
+        <v>726</v>
       </c>
       <c r="F144" s="2">
         <v>9940085134</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>727</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>588</v>
+        <v>729</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>590</v>
+        <v>731</v>
       </c>
       <c r="F145" s="2">
         <v>9528537800</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>732</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="I145" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>592</v>
+        <v>734</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>593</v>
+        <v>735</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>594</v>
+        <v>736</v>
       </c>
       <c r="F146" s="2">
         <v>8438234525</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>737</v>
+      </c>
+      <c r="H146" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="I146" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>596</v>
+        <v>739</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>597</v>
+        <v>740</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>598</v>
+        <v>741</v>
       </c>
       <c r="F147" s="2">
         <v>9566029509</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>742</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="I147" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>600</v>
+        <v>744</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>601</v>
+        <v>745</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>602</v>
+        <v>746</v>
       </c>
       <c r="F148" s="2">
         <v>9941014154</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+        <v>747</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="I148" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J148" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>604</v>
+        <v>749</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>606</v>
+        <v>751</v>
       </c>
       <c r="F149" s="2">
         <v>9176404337</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+        <v>752</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>608</v>
+        <v>754</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>609</v>
+        <v>755</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>610</v>
+        <v>756</v>
       </c>
       <c r="F150" s="2">
         <v>7780198696</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>757</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>612</v>
+        <v>759</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>613</v>
+        <v>760</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>614</v>
+        <v>761</v>
       </c>
       <c r="F151" s="2">
         <v>9094741005</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+        <v>762</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>616</v>
+        <v>764</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>617</v>
+        <v>765</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>618</v>
+        <v>766</v>
       </c>
       <c r="F152" s="2">
         <v>9884020052</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+        <v>767</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="I152" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>620</v>
+        <v>769</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>621</v>
+        <v>770</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>622</v>
+        <v>771</v>
       </c>
       <c r="F153" s="2">
         <v>8148182630</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>772</v>
+      </c>
+      <c r="H153" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="I153" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J153" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>624</v>
+        <v>774</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>625</v>
+        <v>775</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>626</v>
+        <v>776</v>
       </c>
       <c r="F154" s="2">
         <v>7871171706</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+        <v>777</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="I154" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>628</v>
+        <v>779</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>629</v>
+        <v>780</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>630</v>
+        <v>781</v>
       </c>
       <c r="F155" s="2">
         <v>8754412114</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>782</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="I155" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J155" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>632</v>
+        <v>784</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>633</v>
+        <v>785</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>634</v>
+        <v>786</v>
       </c>
       <c r="F156" s="2">
         <v>9677025777</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>787</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>636</v>
+        <v>789</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>637</v>
+        <v>790</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>638</v>
+        <v>791</v>
       </c>
       <c r="F157" s="2">
         <v>9486326998</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>792</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="I157" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J157" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>640</v>
+        <v>794</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>641</v>
+        <v>795</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>642</v>
+        <v>796</v>
       </c>
       <c r="F158" s="2">
         <v>9790931473</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+        <v>797</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>644</v>
+        <v>799</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>645</v>
+        <v>800</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>646</v>
+        <v>801</v>
       </c>
       <c r="F159" s="2">
         <v>9962573944</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>802</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J159" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>648</v>
+        <v>804</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>649</v>
+        <v>805</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>650</v>
+        <v>806</v>
       </c>
       <c r="F160" s="2">
         <v>9307444445</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+        <v>807</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>652</v>
+        <v>809</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>653</v>
+        <v>810</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>654</v>
+        <v>811</v>
       </c>
       <c r="F161" s="2">
         <v>8667742498</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>655</v>
+        <v>812</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="I161" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J161" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G161" xr:uid="{1C94216C-6603-0645-9AE3-ED401F2BACBF}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D42:D55 D57:D59 D61 D122:D156 E157:E161" xr:uid="{9C3BB46B-2E1D-FA4B-BACB-1A35758652BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D42:D55 D57:D59 D61 D122:D156 E157:E161" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Male,Female"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{8799547A-C571-7B47-8167-5C7DB3862A8F}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{49484552-B7C1-E74E-B7C7-CD0288AB9EFB}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{65A0B81F-8241-1E42-8DD1-3DFF9155DB53}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{D0EA16E0-A75F-2542-BA41-72D345E85EE5}"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://www.strava.com/athletes/179130630" xr:uid="{9B7B0B1A-9B5C-A645-A880-4F268C734606}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{D5D646F8-0CF8-D346-8C83-DF685AEB3FAD}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{3FD13486-FC09-A44A-8E6B-094B7AEF9342}"/>
-    <hyperlink ref="G9" r:id="rId8" display="https://www.strava.com/athletes/2042172220" xr:uid="{27652DCA-E6C4-A54A-876C-458B7EAF64D5}"/>
-    <hyperlink ref="G10" r:id="rId9" xr:uid="{C9644049-4F8D-214C-B35E-C4FF4A9884B5}"/>
-    <hyperlink ref="G11" r:id="rId10" xr:uid="{6108F57C-1A46-6A43-A8B1-BAF0BB79385D}"/>
-    <hyperlink ref="G12" r:id="rId11" xr:uid="{E8EC0AE3-03CB-7F4A-A324-AB9350DA2392}"/>
-    <hyperlink ref="G13" r:id="rId12" xr:uid="{34051F85-6D17-5342-B036-48515F4C99EA}"/>
-    <hyperlink ref="G14" r:id="rId13" xr:uid="{8E22113E-54FC-B742-8047-401EA1C585B5}"/>
-    <hyperlink ref="G15" r:id="rId14" xr:uid="{1AA99783-C4EE-1741-B81E-17E391BE4AC7}"/>
-    <hyperlink ref="G16" r:id="rId15" display="https://www.strava.com/athletes/1814695088" xr:uid="{017CCE6A-349E-E649-A52F-D95392DCD9F8}"/>
-    <hyperlink ref="G17" r:id="rId16" xr:uid="{15CE4024-7C44-1748-96B8-A7D3E750C4CB}"/>
-    <hyperlink ref="G18" r:id="rId17" xr:uid="{3933078E-4D12-CB4C-B9D2-CC307FFE3BB8}"/>
-    <hyperlink ref="G19" r:id="rId18" xr:uid="{05B8D2AA-D23A-0044-AE0E-BD0D9BBD3A70}"/>
-    <hyperlink ref="G20" r:id="rId19" xr:uid="{3AC3DF88-11A5-E948-9FC9-039F445FC29E}"/>
-    <hyperlink ref="G21" r:id="rId20" display="https://teams.microsoft.com/l/message/48:notes/1783938684445?context=%7B%22contextType%22%3A%22chat%22%2C%22oid%22%3A%228%3Aorgid%3A1b01d1d8-a803-458e-b38c-c38dec177eea%22%7D" xr:uid="{122E75A7-C3B7-D248-82A9-EC240FF42B3E}"/>
-    <hyperlink ref="G62" r:id="rId21" xr:uid="{F7EE01F4-44BA-C742-B23B-2547553EDB7F}"/>
-    <hyperlink ref="G63" r:id="rId22" xr:uid="{E11FD1BA-02AA-4B4A-A3BA-1AC66F85025C}"/>
-    <hyperlink ref="G64" r:id="rId23" xr:uid="{93B77D29-80E7-3E46-BE61-71E0CC793293}"/>
-    <hyperlink ref="G65" r:id="rId24" xr:uid="{0C1FFC29-3291-D74C-8657-C4E0D7436072}"/>
-    <hyperlink ref="G66" r:id="rId25" xr:uid="{9ABC1D4A-5DB7-DB4A-9B10-1393CBC2C012}"/>
-    <hyperlink ref="G67" r:id="rId26" xr:uid="{89AB7CFE-3439-FE42-BF4E-1C854EB79DE3}"/>
-    <hyperlink ref="G68" r:id="rId27" xr:uid="{CF7C3668-BBE4-EB4A-A455-7667FD776253}"/>
-    <hyperlink ref="G69" r:id="rId28" xr:uid="{AD769B27-9C96-0245-AC3D-E545A51E3EF0}"/>
-    <hyperlink ref="G70" r:id="rId29" xr:uid="{673ED919-953C-4740-B068-4936E05BCFAC}"/>
-    <hyperlink ref="G71" r:id="rId30" xr:uid="{13EE8B1A-7A19-2C4C-B99F-0845F8B86164}"/>
-    <hyperlink ref="G72" r:id="rId31" xr:uid="{F42BB128-C1DA-0F48-99D1-5BCD52A4D534}"/>
-    <hyperlink ref="G73" r:id="rId32" xr:uid="{DF600DA8-0AE0-984B-A38F-A548EEE16C35}"/>
-    <hyperlink ref="G74" r:id="rId33" xr:uid="{8839BBE7-6566-6C4A-AA8D-367C4A369CB6}"/>
-    <hyperlink ref="G75" r:id="rId34" xr:uid="{AE7F1E7B-B64F-2D43-8283-9A919670F2CD}"/>
-    <hyperlink ref="G76" r:id="rId35" xr:uid="{5CD337FE-652A-7440-8514-9DAB566F7609}"/>
-    <hyperlink ref="G77" r:id="rId36" xr:uid="{7C5F25B0-1656-AB46-8BBB-56C489D9CC58}"/>
-    <hyperlink ref="G78" r:id="rId37" xr:uid="{4EED48B2-30B1-8A46-87CE-1811CDE058F2}"/>
-    <hyperlink ref="G79" r:id="rId38" xr:uid="{2378E63B-DADE-AC43-A6E6-4662F5383590}"/>
-    <hyperlink ref="G80" r:id="rId39" xr:uid="{16973CD8-6B26-7B4F-9272-0F64BA5F4594}"/>
-    <hyperlink ref="G81" r:id="rId40" xr:uid="{5775D902-1F4F-1648-A114-526AFC3A728D}"/>
-    <hyperlink ref="G82" r:id="rId41" xr:uid="{48054A84-F8A7-9A4F-BD7B-0FE073480420}"/>
-    <hyperlink ref="G83" r:id="rId42" xr:uid="{B20E11F7-ACBC-F944-9B2B-E75CF21F1325}"/>
-    <hyperlink ref="G84" r:id="rId43" xr:uid="{43FBBE68-3997-4C48-A07B-17A3D73C4278}"/>
-    <hyperlink ref="G85" r:id="rId44" xr:uid="{A1AFC7BF-8F8A-DD4E-A1A3-7D897DCB8BE6}"/>
-    <hyperlink ref="G86" r:id="rId45" xr:uid="{FF85354C-EF2A-154D-9E6A-B7158C2CB0B7}"/>
-    <hyperlink ref="G87" r:id="rId46" xr:uid="{289D92BC-AB39-1847-9954-A1EA68D93729}"/>
-    <hyperlink ref="G88" r:id="rId47" xr:uid="{F2AD07BE-2EC3-F642-9F77-94654678B078}"/>
-    <hyperlink ref="G89" r:id="rId48" xr:uid="{C7FB7EB6-F88C-3D44-92D7-ACA531825BF4}"/>
-    <hyperlink ref="G90" r:id="rId49" xr:uid="{E2EACBB0-59B8-0B40-88B0-9FB4F0C7483B}"/>
-    <hyperlink ref="G91" r:id="rId50" xr:uid="{415124FE-7A9F-B74F-BD91-AC1AF6C01753}"/>
-    <hyperlink ref="G92" r:id="rId51" xr:uid="{7634BA1D-31A8-B545-8CFA-40F9DDD493E4}"/>
-    <hyperlink ref="G93" r:id="rId52" xr:uid="{927879B1-394A-9D4C-B5B4-F15F6D3DC280}"/>
-    <hyperlink ref="G94" r:id="rId53" xr:uid="{BD4FFD04-6D31-5648-97A5-E76D435F2DCE}"/>
-    <hyperlink ref="G95" r:id="rId54" xr:uid="{9A26B3EC-9278-F74B-9DAB-A891974D846A}"/>
-    <hyperlink ref="G96" r:id="rId55" xr:uid="{3D49B066-8E3A-8346-8FDA-3A626952B9CF}"/>
-    <hyperlink ref="G97" r:id="rId56" xr:uid="{3980EBF8-1C72-4B45-935D-DCD83D723B1E}"/>
-    <hyperlink ref="G98" r:id="rId57" xr:uid="{0FD4A77A-02B7-EC46-9E32-E9E84E1B2875}"/>
-    <hyperlink ref="E99" r:id="rId58" display="mailto:krish.shrikrish@ericsson.com" xr:uid="{10B98C7A-2978-3342-BEA2-37AC2141C886}"/>
-    <hyperlink ref="G99" r:id="rId59" xr:uid="{ED9231EA-F3D5-7240-B361-33252522453D}"/>
-    <hyperlink ref="G100" r:id="rId60" xr:uid="{FAF2CFF5-7CA1-1240-BE3E-81AFD8C3F1F7}"/>
-    <hyperlink ref="G101" r:id="rId61" xr:uid="{6570BD1D-9DE1-0A47-A05A-AA0A1D8CB79B}"/>
-    <hyperlink ref="G102" r:id="rId62" xr:uid="{8A668E29-FA4D-A54C-BA8F-93ED69B579E0}"/>
-    <hyperlink ref="E103" r:id="rId63" display="mailto:chandani.parachuri@ericsson.com" xr:uid="{D93CB29E-EE0E-A347-AC7C-5527B1C751A3}"/>
-    <hyperlink ref="G103" r:id="rId64" xr:uid="{58847BF4-F9F3-8841-916A-7AADCF3E0014}"/>
-    <hyperlink ref="E104" r:id="rId65" display="mailto:n.vinuja@ericsson.com" xr:uid="{1F7724AE-DA01-C841-AD93-7CAC34B17FED}"/>
-    <hyperlink ref="G104" r:id="rId66" xr:uid="{485A2229-B126-F14B-A06C-8249115D9139}"/>
-    <hyperlink ref="E105" r:id="rId67" display="mailto:kamalakannan.s@ericsson.com" xr:uid="{9877F1A8-49C9-EE42-B139-E83E51522D44}"/>
-    <hyperlink ref="G105" r:id="rId68" display="https://strava.app.link/ovgIsMaWJ4b" xr:uid="{FC5902DD-21BE-CC40-ADC4-2A4D0B3E8E79}"/>
-    <hyperlink ref="G106" r:id="rId69" xr:uid="{5E1601F8-B8A9-4D42-82D2-F48FB2E4F47A}"/>
-    <hyperlink ref="G107" r:id="rId70" xr:uid="{FD6372CD-295D-0E4B-8757-F73E05CE059C}"/>
-    <hyperlink ref="E108" r:id="rId71" display="mailto:kranthi.kumar.s@ericsson.com" xr:uid="{FC1B4B0A-2DCB-804E-9DC5-DF3EAA0E5DDF}"/>
-    <hyperlink ref="G108" r:id="rId72" xr:uid="{BB0EC8BE-88A3-1F44-BEAA-F9310EEEE798}"/>
-    <hyperlink ref="E109" r:id="rId73" display="mailto:sarathypartha416@gmail.com" xr:uid="{F76963EC-40B2-004F-801E-7A6921F76637}"/>
-    <hyperlink ref="G109" r:id="rId74" display="https://www.strava.com/athletes/1570233933" xr:uid="{FDAFA3AA-4132-2F45-8027-3FDAD21FD2D5}"/>
-    <hyperlink ref="G110" r:id="rId75" xr:uid="{29ED1EAA-50A7-244C-804D-BB487FE40B97}"/>
-    <hyperlink ref="G111" r:id="rId76" display="https://strava.app.link/ezjCSrlZJ4b" xr:uid="{8E7B88D8-129E-F047-9868-CF89491D5FBB}"/>
-    <hyperlink ref="E112" r:id="rId77" display="mailto:balapoornima@gmail.com" xr:uid="{369AA7FB-38A4-7445-BA55-9B6BB8567AC0}"/>
-    <hyperlink ref="G112" r:id="rId78" xr:uid="{C4D267BF-E525-8343-8CBB-28F91A3A195C}"/>
-    <hyperlink ref="E113" r:id="rId79" display="mailto:sowmyagajendiran123@gmail.com" xr:uid="{2CAF6323-EA8D-F747-9710-0C343B85BC10}"/>
-    <hyperlink ref="G113" r:id="rId80" xr:uid="{BC21D94E-944F-FF47-87B5-365CF96B9774}"/>
-    <hyperlink ref="E114" r:id="rId81" display="mailto:lohithaa.k.m@ericsson.com" xr:uid="{617EB69B-3189-CA4F-935F-CDAF7CD22BEC}"/>
-    <hyperlink ref="G114" r:id="rId82" xr:uid="{09E0785C-EA75-1242-B72A-9AD15C9708A9}"/>
-    <hyperlink ref="E115" r:id="rId83" display="mailto:ganti.alekhya@ericsson.com" xr:uid="{8DE591FC-1392-2D47-BF2E-BDA035C21AFC}"/>
-    <hyperlink ref="G115" r:id="rId84" xr:uid="{F51D6A2E-E36B-8046-A6C0-24AAA90BBBB5}"/>
-    <hyperlink ref="G116" r:id="rId85" xr:uid="{3E63F5CE-A7A3-4A44-B94F-207D36949B13}"/>
-    <hyperlink ref="E117" r:id="rId86" display="mailto:praveen.shanmugam@ericsson.com" xr:uid="{C4DF13E3-3E02-9847-B810-B7CE2CBC5A7C}"/>
-    <hyperlink ref="G117" r:id="rId87" xr:uid="{EBBA9B27-B98E-D842-A10E-D73BF687B33F}"/>
-    <hyperlink ref="E118" r:id="rId88" display="mailto:prasanna.kalyanasundaram@ericsson.com" xr:uid="{05C3AFCD-CC53-9646-B039-7031CED6C658}"/>
-    <hyperlink ref="E119" r:id="rId89" display="mailto:selva.muthu.kumaran.ext@ericsson.com" xr:uid="{E89C7E69-FB43-F746-B4D6-93023B1DC953}"/>
-    <hyperlink ref="G119" r:id="rId90" xr:uid="{B0FDD064-0210-D044-A5BF-2904F46D595A}"/>
-    <hyperlink ref="G120" r:id="rId91" xr:uid="{A4334BC2-7301-8944-8614-6817BAC10114}"/>
-    <hyperlink ref="G121" r:id="rId92" xr:uid="{DA21DB8C-B857-5D4B-8BEF-7D897C28FA76}"/>
-    <hyperlink ref="G24" r:id="rId93" xr:uid="{9BD3FE2E-0EDF-A140-B904-F66939366E74}"/>
-    <hyperlink ref="G25" r:id="rId94" xr:uid="{865BF8CA-5836-E041-BBF4-A0CFF2B01592}"/>
-    <hyperlink ref="G26" r:id="rId95" xr:uid="{6C2701AD-0316-7B40-B5CB-08BEE8E2F6DA}"/>
-    <hyperlink ref="G28" r:id="rId96" xr:uid="{6652C5B9-9EC5-314D-893E-B5AA0CCC8C6A}"/>
-    <hyperlink ref="G29" r:id="rId97" xr:uid="{3B3F246C-E5B9-6D43-8ACE-AB519BAC97AC}"/>
-    <hyperlink ref="G31" r:id="rId98" xr:uid="{00277B89-AFCE-2347-80E4-BEA7722352EB}"/>
-    <hyperlink ref="G27" r:id="rId99" xr:uid="{8B9A7E53-0F94-F147-84C6-C834ED484C7E}"/>
-    <hyperlink ref="G34" r:id="rId100" xr:uid="{62AC31C8-F5D5-AA48-BCFD-218FA85C7182}"/>
-    <hyperlink ref="G22" r:id="rId101" xr:uid="{B65DB6B1-7ED9-9649-BDC6-DAD8E0F5BC7E}"/>
-    <hyperlink ref="G36" r:id="rId102" xr:uid="{BD0B6A15-10D6-444B-AC51-E79D825818C3}"/>
-    <hyperlink ref="G35" r:id="rId103" xr:uid="{A8463560-7C21-6C40-9622-56F140D28CC1}"/>
-    <hyperlink ref="G32" r:id="rId104" xr:uid="{D0C7E7A1-A56F-2748-9419-30B464418D12}"/>
-    <hyperlink ref="G30" r:id="rId105" xr:uid="{C240782D-0B17-6A46-8255-36815AC33A9C}"/>
-    <hyperlink ref="G39" r:id="rId106" xr:uid="{58DB0A19-A280-F342-B667-D3CF74759A1A}"/>
-    <hyperlink ref="G37" r:id="rId107" xr:uid="{D1AE2187-FF16-744C-ABFC-31F57C7715CC}"/>
-    <hyperlink ref="G33" r:id="rId108" xr:uid="{C3066C53-581D-DA4C-B65F-6ADEB28B3CC8}"/>
-    <hyperlink ref="G23" r:id="rId109" xr:uid="{0E742BCD-9108-F345-ADD9-B2C10A006B51}"/>
-    <hyperlink ref="G38" r:id="rId110" xr:uid="{C6A10172-856A-A342-9F64-0F1D5C5BBF3D}"/>
-    <hyperlink ref="G40" r:id="rId111" xr:uid="{6F295809-0DD4-1649-A1AE-7F3B7198CDFD}"/>
-    <hyperlink ref="G41" r:id="rId112" xr:uid="{AE591982-B8CC-D640-8B9E-25120D9974F4}"/>
-    <hyperlink ref="E42" r:id="rId113" xr:uid="{22B07373-DC2C-4940-B139-FB4908BD240C}"/>
-    <hyperlink ref="G42" r:id="rId114" xr:uid="{B9B6EC67-2DD9-8D41-A83D-D3B0CED7157F}"/>
-    <hyperlink ref="E43" r:id="rId115" xr:uid="{B7C146AA-0D5B-534A-9F3A-A6992C84C05B}"/>
-    <hyperlink ref="E45" r:id="rId116" xr:uid="{EE51A689-343C-EE42-A6E0-18030702E62A}"/>
-    <hyperlink ref="G45" r:id="rId117" xr:uid="{0498EA8A-52D9-AB4B-870A-CBE84BE19705}"/>
-    <hyperlink ref="E44" r:id="rId118" xr:uid="{70CAD6B3-89A5-EE43-8286-FF7FEA4F2D6B}"/>
-    <hyperlink ref="G44" r:id="rId119" xr:uid="{261D3E5C-ABDF-2747-8A23-3CF34F9B7CD4}"/>
-    <hyperlink ref="G43" r:id="rId120" xr:uid="{42EA60DD-B365-B944-A8E9-C94C66DBCD07}"/>
-    <hyperlink ref="E46" r:id="rId121" xr:uid="{54A4E9E3-0897-A747-917C-6B597B0C984C}"/>
-    <hyperlink ref="E47" r:id="rId122" xr:uid="{BE7B9B3E-96B6-B94F-83F8-F7A2F08BB884}"/>
-    <hyperlink ref="G47" r:id="rId123" xr:uid="{740930E3-97DB-DE44-B586-42488666C0E5}"/>
-    <hyperlink ref="G46" r:id="rId124" xr:uid="{53CE9C7C-916D-D440-BE1A-C177067B86C9}"/>
-    <hyperlink ref="E48" r:id="rId125" xr:uid="{A1141E8B-CBE4-F24F-8175-A56819860D5A}"/>
-    <hyperlink ref="E49" r:id="rId126" xr:uid="{306BC68B-0B29-0B4D-B81E-FFEF895AC43E}"/>
-    <hyperlink ref="G48" r:id="rId127" xr:uid="{7BC85781-223F-5F47-A843-52CFFC39D84F}"/>
-    <hyperlink ref="E50" r:id="rId128" xr:uid="{8B911D1D-3659-264F-9844-EA3ED4982986}"/>
-    <hyperlink ref="G50" r:id="rId129" xr:uid="{AF3C7EE8-4337-8643-AA67-8821624FCBF7}"/>
-    <hyperlink ref="E51" r:id="rId130" xr:uid="{1A1BB30F-54BF-A44C-BB18-1EE844964B4D}"/>
-    <hyperlink ref="E52" r:id="rId131" xr:uid="{AC51E600-669C-4F4C-8E88-34F0EB35B39E}"/>
-    <hyperlink ref="G52" r:id="rId132" xr:uid="{C5A0D69A-BB61-DE4C-A313-0F8827DEA15D}"/>
-    <hyperlink ref="E53" r:id="rId133" xr:uid="{9BFDCC89-4C46-7E41-8B39-63271973B7EC}"/>
-    <hyperlink ref="G49" r:id="rId134" xr:uid="{C0E803E4-7364-E948-AB9F-8A5787654852}"/>
-    <hyperlink ref="G53" r:id="rId135" xr:uid="{F7376ECB-0F61-324E-AE42-90E17E5F5669}"/>
-    <hyperlink ref="G51" r:id="rId136" xr:uid="{71EE6C6A-B81B-EA44-918A-98E213E63DD9}"/>
-    <hyperlink ref="E54" r:id="rId137" xr:uid="{D63E1303-BF76-9A4B-A470-8C4D9408CEAB}"/>
-    <hyperlink ref="G54" r:id="rId138" xr:uid="{A8C33064-4D8C-D648-99E0-6C2D6646461A}"/>
-    <hyperlink ref="E55" r:id="rId139" xr:uid="{12A12D87-F950-324A-BAAB-F903ABD12E84}"/>
-    <hyperlink ref="G55" r:id="rId140" xr:uid="{4F89DAF5-CAC5-CA46-9788-F5AFA02A129F}"/>
-    <hyperlink ref="E61" r:id="rId141" xr:uid="{D0C07CCC-723C-4C42-B4CC-E80D8474D070}"/>
-    <hyperlink ref="G61" r:id="rId142" xr:uid="{93009846-F45D-7D40-B181-120EA9221A01}"/>
-    <hyperlink ref="E57" r:id="rId143" xr:uid="{64AE02CC-714C-7A46-93A2-6FEC7731D241}"/>
-    <hyperlink ref="G57" r:id="rId144" xr:uid="{CA95DE4A-79DB-7042-8C50-3C8648F74889}"/>
-    <hyperlink ref="E59" r:id="rId145" xr:uid="{E1441FC6-3946-3A4C-B202-1F6F6867ADA1}"/>
-    <hyperlink ref="G59" r:id="rId146" xr:uid="{DF755855-0856-A74B-9D6C-29D1AFDE31B2}"/>
-    <hyperlink ref="E58" r:id="rId147" xr:uid="{92A69C7E-1DAC-0648-A6A3-A7FDBE8334D4}"/>
-    <hyperlink ref="G58" r:id="rId148" xr:uid="{6B2CCA56-F8A8-354A-ACBC-1CDE646C8857}"/>
-    <hyperlink ref="E60" r:id="rId149" xr:uid="{5792A0D4-6A4A-0744-A1EA-61E0120C8C71}"/>
-    <hyperlink ref="G60" r:id="rId150" xr:uid="{AEE29409-DD1C-1D4B-8147-FD2F4F46DF95}"/>
-    <hyperlink ref="E56" r:id="rId151" display="mailto:prason.poudel@ericsson.com" xr:uid="{5548FB7F-BD0A-514B-AF2A-FFBE28D73DDA}"/>
-    <hyperlink ref="G56" r:id="rId152" xr:uid="{14959EFB-170D-3247-A6C9-BF087CF477BD}"/>
-    <hyperlink ref="G142" r:id="rId153" tooltip="https://strava.app.link/bwltfpa7j4b" xr:uid="{E6F2548A-5714-7545-B2DC-47D7E411EB8D}"/>
-    <hyperlink ref="G148" r:id="rId154" xr:uid="{0DA5F9BE-B537-B642-A91F-3B0CB33EB2DE}"/>
-    <hyperlink ref="G146" r:id="rId155" xr:uid="{11D14BEF-B396-B949-95D7-4FD967CEC1A0}"/>
-    <hyperlink ref="G155" r:id="rId156" xr:uid="{210C1D2C-5562-7B46-BE32-BAF565303283}"/>
-    <hyperlink ref="G147" r:id="rId157" xr:uid="{DA134629-E937-444F-8DC4-1379C0E86E6F}"/>
-    <hyperlink ref="G161" r:id="rId158" xr:uid="{258901D9-5E49-A74E-8B70-149524C72329}"/>
-    <hyperlink ref="G144" r:id="rId159" xr:uid="{245E1ABB-1388-794E-A2AE-9F86E4308DEA}"/>
-    <hyperlink ref="G159" r:id="rId160" xr:uid="{8E105EEA-8F81-B940-BC07-F705D6E0C85F}"/>
-    <hyperlink ref="G143" r:id="rId161" xr:uid="{4FC6E46D-1358-C440-A3E0-3D2EEDCE4207}"/>
-    <hyperlink ref="G149" r:id="rId162" xr:uid="{3C344BE2-222D-044E-9F6E-F41697CC2EAC}"/>
-    <hyperlink ref="G160" r:id="rId163" xr:uid="{24B4B9C4-5269-A446-9DF7-9B20EC26D6A3}"/>
-    <hyperlink ref="G151" r:id="rId164" xr:uid="{64A0E0B9-361F-514D-AA42-CC27BB2A0101}"/>
-    <hyperlink ref="G157" r:id="rId165" xr:uid="{F4A786A2-9F04-E94D-A6EE-90C0A0D0496F}"/>
-    <hyperlink ref="G145" r:id="rId166" xr:uid="{08CC8C0C-62E1-F64F-98BE-1FFAF7DCFF4F}"/>
-    <hyperlink ref="G158" r:id="rId167" xr:uid="{4EF07843-CFD8-6C49-83A8-77009542E61F}"/>
-    <hyperlink ref="G153" r:id="rId168" xr:uid="{BB655932-C099-E542-85C1-08B639769888}"/>
-    <hyperlink ref="G152" r:id="rId169" xr:uid="{54359897-1AF3-C240-A636-6F0715FE0779}"/>
-    <hyperlink ref="G156" r:id="rId170" xr:uid="{D74836F8-4738-EF45-873B-D296216D55F2}"/>
-    <hyperlink ref="G150" r:id="rId171" xr:uid="{EF83C4BA-BD70-F843-B84C-D1FB321BD223}"/>
-    <hyperlink ref="G154" r:id="rId172" xr:uid="{D163334A-F189-5C4E-B5F8-005F17EEEC1E}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.strava.com/athletes/179130630" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G9" r:id="rId8" display="https://www.strava.com/athletes/2042172220" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G16" r:id="rId15" display="https://www.strava.com/athletes/1814695088" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G21" r:id="rId20" display="https://teams.microsoft.com/l/message/48:notes/1783938684445?context=%7B%22contextType%22%3A%22chat%22%2C%22oid%22%3A%228%3Aorgid%3A1b01d1d8-a803-458e-b38c-c38dec177eea%22%7D" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="G28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="G30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="G31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="G32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="G33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="G34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="G35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="G36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="G37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="G38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="G39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="G40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="G41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="E42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="G42" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="E43" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="G43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="G44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="E45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="G45" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="E46" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="G46" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="E47" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="G47" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="E48" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="G48" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="E49" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="G49" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="E50" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="G50" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="E51" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="G51" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="E52" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="G52" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="E53" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="G53" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="E54" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="G54" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="E55" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="G55" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="E56" r:id="rId69" display="mailto:prason.poudel@ericsson.com" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="G56" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="E57" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="G57" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="E58" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="G58" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="E59" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="G59" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="E60" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="G60" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="E61" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="G61" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="G62" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="G63" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="G64" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="G65" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="G66" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="G67" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="G68" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="G69" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="G70" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="G71" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="G72" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="G73" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="G74" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="G75" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="G76" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="G77" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="G78" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="G79" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="G80" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="G81" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="G82" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="G83" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="G84" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="G85" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="G86" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="G87" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="G88" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="G89" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="G90" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="G91" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="G92" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="G93" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="G94" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="G95" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="G96" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="G97" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="G98" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="E99" r:id="rId118" display="mailto:krish.shrikrish@ericsson.com" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="G99" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="G100" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="G101" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="G102" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="E103" r:id="rId123" display="mailto:chandani.parachuri@ericsson.com" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="G103" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="E104" r:id="rId125" display="mailto:n.vinuja@ericsson.com" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="G104" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="E105" r:id="rId127" display="mailto:kamalakannan.s@ericsson.com" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="G105" r:id="rId128" display="https://strava.app.link/ovgIsMaWJ4b" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="G106" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="G107" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="E108" r:id="rId131" display="mailto:kranthi.kumar.s@ericsson.com" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="G108" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="E109" r:id="rId133" display="mailto:sarathypartha416@gmail.com" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="G109" r:id="rId134" display="https://www.strava.com/athletes/1570233933" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="G110" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="G111" r:id="rId136" display="https://strava.app.link/ezjCSrlZJ4b" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="E112" r:id="rId137" display="mailto:balapoornima@gmail.com" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="G112" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="E113" r:id="rId139" display="mailto:sowmyagajendiran123@gmail.com" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="G113" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="E114" r:id="rId141" display="mailto:lohithaa.k.m@ericsson.com" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="G114" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="E115" r:id="rId143" display="mailto:ganti.alekhya@ericsson.com" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="G115" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="G116" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="E117" r:id="rId146" display="mailto:praveen.shanmugam@ericsson.com" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="G117" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="E118" r:id="rId148" display="mailto:prasanna.kalyanasundaram@ericsson.com" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="E119" r:id="rId149" display="mailto:selva.muthu.kumaran.ext@ericsson.com" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="G119" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="G120" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="G121" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="G142" r:id="rId153" tooltip="https://strava.app.link/bwltfpa7j4b" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="G143" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="G144" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="G145" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="G146" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="G147" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="G148" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="G149" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="G150" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="G151" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="G152" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="G153" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="G154" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="G155" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="G156" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="G157" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="G158" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="G159" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="G160" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="G161" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{92e84ceb-fbfd-47ab-be52-080c6b87953f}" enabled="0" method="" siteId="{92e84ceb-fbfd-47ab-be52-080c6b87953f}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/Walkathon Nominations 2026_Final.xlsx
+++ b/Walkathon Nominations 2026_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epxxvis/projects/walky/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B743D15-485E-FC47-803E-873F70C39BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC79A41-C506-BC49-9845-EDC7313BD705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$H$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$J$161</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="813">
   <si>
     <t>Team Name</t>
   </si>
@@ -1625,9 +1625,6 @@
   </si>
   <si>
     <t>Kamalakannan Sudhakar | Strava Athlete Profile</t>
-  </si>
-  <si>
-    <t>Unassigned</t>
   </si>
   <si>
     <t>ZMANRAO</t>
@@ -2930,6 +2927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2978,7 +2976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
@@ -3010,7 +3008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -3074,7 +3072,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -3106,7 +3104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
@@ -3138,7 +3136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -3170,7 +3168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -3202,7 +3200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -3234,7 +3232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -3266,7 +3264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -3298,7 +3296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -3330,7 +3328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -3362,7 +3360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
@@ -3394,7 +3392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
@@ -3490,7 +3488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>10</v>
       </c>
@@ -3522,7 +3520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>10</v>
       </c>
@@ -3554,7 +3552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>10</v>
       </c>
@@ -3586,7 +3584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>10</v>
       </c>
@@ -3618,7 +3616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>114</v>
       </c>
@@ -3650,7 +3648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>114</v>
       </c>
@@ -3682,7 +3680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>114</v>
       </c>
@@ -3714,7 +3712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>114</v>
       </c>
@@ -3746,7 +3744,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>114</v>
       </c>
@@ -3810,7 +3808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>114</v>
       </c>
@@ -3842,7 +3840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>114</v>
       </c>
@@ -3874,7 +3872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>114</v>
       </c>
@@ -3906,7 +3904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>114</v>
       </c>
@@ -3938,7 +3936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>114</v>
       </c>
@@ -4002,7 +4000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
@@ -4034,7 +4032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>114</v>
       </c>
@@ -4066,7 +4064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>114</v>
       </c>
@@ -4098,7 +4096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>114</v>
       </c>
@@ -4130,7 +4128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>114</v>
       </c>
@@ -4162,7 +4160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>114</v>
       </c>
@@ -4226,7 +4224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>114</v>
       </c>
@@ -4258,7 +4256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>213</v>
       </c>
@@ -4322,7 +4320,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>213</v>
       </c>
@@ -4674,7 +4672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>213</v>
       </c>
@@ -4770,7 +4768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>213</v>
       </c>
@@ -4930,7 +4928,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>312</v>
       </c>
@@ -5026,7 +5024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>312</v>
       </c>
@@ -5090,7 +5088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>312</v>
       </c>
@@ -5186,7 +5184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>312</v>
       </c>
@@ -5314,7 +5312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>312</v>
       </c>
@@ -5346,7 +5344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>312</v>
       </c>
@@ -5506,7 +5504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>312</v>
       </c>
@@ -5538,7 +5536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>413</v>
       </c>
@@ -5570,7 +5568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>413</v>
       </c>
@@ -5666,7 +5664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>413</v>
       </c>
@@ -5698,7 +5696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>413</v>
       </c>
@@ -5730,7 +5728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>413</v>
       </c>
@@ -5762,7 +5760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>413</v>
       </c>
@@ -5826,7 +5824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>413</v>
       </c>
@@ -5890,7 +5888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>413</v>
       </c>
@@ -5954,7 +5952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>413</v>
       </c>
@@ -5986,7 +5984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>413</v>
       </c>
@@ -6018,7 +6016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>413</v>
       </c>
@@ -6050,7 +6048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>413</v>
       </c>
@@ -6082,7 +6080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>413</v>
       </c>
@@ -6178,7 +6176,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>514</v>
       </c>
@@ -6210,7 +6208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>514</v>
       </c>
@@ -6242,7 +6240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>514</v>
       </c>
@@ -6274,7 +6272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>514</v>
       </c>
@@ -6303,33 +6301,33 @@
         <v>29</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
         <v>536</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>537</v>
       </c>
       <c r="F106" s="2">
         <v>9985541711</v>
       </c>
       <c r="G106" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="H106" s="10" t="s">
         <v>538</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>539</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>17</v>
@@ -6343,25 +6341,25 @@
         <v>514</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="F107" s="2">
         <v>919841248577</v>
       </c>
       <c r="G107" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>543</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>544</v>
       </c>
       <c r="I107" s="10" t="s">
         <v>29</v>
@@ -6370,30 +6368,30 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="D108" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="7" t="s">
         <v>546</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>547</v>
       </c>
       <c r="F108" s="2">
         <v>919500074227</v>
       </c>
       <c r="G108" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="H108" s="10" t="s">
         <v>548</v>
-      </c>
-      <c r="H108" s="10" t="s">
-        <v>549</v>
       </c>
       <c r="I108" s="10" t="s">
         <v>17</v>
@@ -6407,22 +6405,22 @@
         <v>514</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="7" t="s">
         <v>551</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>552</v>
       </c>
       <c r="F109" s="2">
         <v>6382811325</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H109" s="10">
         <v>1570233933</v>
@@ -6434,30 +6432,30 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="F110" s="2">
         <v>919600199456</v>
       </c>
       <c r="G110" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="H110" s="10" t="s">
         <v>557</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>558</v>
       </c>
       <c r="I110" s="10" t="s">
         <v>17</v>
@@ -6471,25 +6469,25 @@
         <v>514</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F111" s="2">
         <v>918939833531</v>
       </c>
       <c r="G111" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>562</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>563</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>29</v>
@@ -6498,30 +6496,30 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F112" s="2">
         <v>9958777360</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="H112" s="10" t="s">
         <v>567</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>568</v>
       </c>
       <c r="I112" s="10" t="s">
         <v>17</v>
@@ -6535,25 +6533,25 @@
         <v>514</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F113" s="2">
         <v>9894916995</v>
       </c>
       <c r="G113" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>573</v>
       </c>
       <c r="I113" s="10" t="s">
         <v>29</v>
@@ -6562,30 +6560,30 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F114" s="2">
         <v>9500043735</v>
       </c>
       <c r="G114" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="H114" s="10" t="s">
         <v>577</v>
-      </c>
-      <c r="H114" s="10" t="s">
-        <v>578</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>17</v>
@@ -6599,25 +6597,25 @@
         <v>514</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F115" s="2">
         <v>6369326376</v>
       </c>
       <c r="G115" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>582</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>583</v>
       </c>
       <c r="I115" s="10" t="s">
         <v>29</v>
@@ -6626,31 +6624,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D116" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="F116" s="2">
         <v>9003724569</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="H116" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="H116" s="10" t="s">
-        <v>588</v>
-      </c>
       <c r="I116" s="10" t="s">
         <v>17</v>
       </c>
@@ -6658,31 +6656,31 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="D117" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="7" t="s">
         <v>590</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>591</v>
       </c>
       <c r="F117" s="2">
         <v>9894540684</v>
       </c>
       <c r="G117" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="H117" s="10" t="s">
-        <v>593</v>
-      </c>
       <c r="I117" s="10" t="s">
         <v>17</v>
       </c>
@@ -6690,31 +6688,31 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="D118" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>595</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>596</v>
       </c>
       <c r="F118" s="2">
         <v>9789810530</v>
       </c>
       <c r="G118" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="H118" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="H118" s="10" t="s">
-        <v>598</v>
-      </c>
       <c r="I118" s="10" t="s">
         <v>17</v>
       </c>
@@ -6722,31 +6720,31 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="D119" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>600</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>601</v>
       </c>
       <c r="F119" s="2">
         <v>9551635956</v>
       </c>
       <c r="G119" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="H119" s="10" t="s">
-        <v>603</v>
-      </c>
       <c r="I119" s="10" t="s">
         <v>17</v>
       </c>
@@ -6754,30 +6752,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F120" s="2">
         <v>919884025540</v>
       </c>
       <c r="G120" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="H120" s="10" t="s">
         <v>607</v>
-      </c>
-      <c r="H120" s="10" t="s">
-        <v>608</v>
       </c>
       <c r="I120" s="10" t="s">
         <v>17</v>
@@ -6791,25 +6789,25 @@
         <v>514</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F121" s="2">
         <v>919677333273</v>
       </c>
       <c r="G121" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>612</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>613</v>
       </c>
       <c r="I121" s="10" t="s">
         <v>29</v>
@@ -6818,447 +6816,447 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="D122" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="F122" s="2">
         <v>8754129067</v>
       </c>
       <c r="G122" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="H122" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="H122" s="10" t="s">
+      <c r="I122" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="I122" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J122" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B123" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="D123" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="F123" s="2">
         <v>8144368800</v>
       </c>
       <c r="G123" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="H123" s="10" t="s">
+      <c r="I123" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="I123" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J123" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="D124" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="F124" s="2">
         <v>9842756727</v>
       </c>
       <c r="G124" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="H124" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="H124" s="10" t="s">
+      <c r="I124" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="I124" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J124" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F125" s="2">
         <v>9488833626</v>
       </c>
       <c r="G125" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="H125" s="10" t="s">
+      <c r="I125" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="I125" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J125" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="D126" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="F126" s="2">
         <v>7382432136</v>
       </c>
       <c r="G126" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="H126" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="H126" s="10" t="s">
+      <c r="I126" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="I126" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J126" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="D127" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="F127" s="2">
         <v>9842956552</v>
       </c>
       <c r="G127" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="H127" s="10" t="s">
+      <c r="I127" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="I127" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J127" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F128" s="2">
         <v>9790998583</v>
       </c>
       <c r="G128" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="H128" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="H128" s="10" t="s">
+      <c r="I128" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="I128" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J128" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="D129" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="F129" s="2">
         <v>9123521909</v>
       </c>
       <c r="G129" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="H129" s="10" t="s">
+      <c r="I129" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="I129" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J129" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="D130" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F130" s="2">
         <v>9790909930</v>
       </c>
       <c r="G130" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="H130" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="H130" s="10" t="s">
+      <c r="I130" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="I130" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J130" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="F131" s="2">
         <v>9843451933</v>
       </c>
       <c r="G131" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H131" s="10" t="s">
+      <c r="I131" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="I131" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J131" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="F132" s="2">
         <v>9940182025</v>
       </c>
       <c r="G132" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="H132" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="H132" s="10" t="s">
+      <c r="I132" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="I132" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J132" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F133" s="2">
         <v>9092487649</v>
       </c>
       <c r="G133" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="H133" s="10" t="s">
+      <c r="I133" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="I133" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J133" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="F134" s="2">
         <v>9900487944</v>
       </c>
       <c r="G134" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="H134" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="H134" s="10" t="s">
+      <c r="I134" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="I134" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J134" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="D135" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="F135" s="2">
         <v>9751234404</v>
       </c>
       <c r="G135" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="H135" s="10" t="s">
-        <v>624</v>
-      </c>
       <c r="I135" s="10" t="s">
         <v>17</v>
       </c>
@@ -7266,414 +7264,414 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="D136" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="F136" s="2">
         <v>9944194100</v>
       </c>
       <c r="G136" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="H136" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="H136" s="10" t="s">
+      <c r="I136" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="I136" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J136" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F137" s="2">
         <v>6361759520</v>
       </c>
       <c r="G137" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="H137" s="10" t="s">
+      <c r="I137" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="I137" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J137" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="F138" s="2">
         <v>8376014306</v>
       </c>
       <c r="G138" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="H138" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="H138" s="10" t="s">
+      <c r="I138" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="I138" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J138" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F139" s="2">
         <v>9790766914</v>
       </c>
       <c r="G139" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>701</v>
       </c>
-      <c r="H139" s="10" t="s">
+      <c r="I139" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="I139" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J139" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="D140" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="F140" s="2">
         <v>9841255581</v>
       </c>
       <c r="G140" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="H140" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="H140" s="10" t="s">
+      <c r="I140" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="I140" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J140" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="D141" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="F141" s="2">
         <v>9843451933</v>
       </c>
       <c r="G141" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="H141" s="10" t="s">
+      <c r="I141" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="I141" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J141" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="2" t="s">
+      <c r="B142" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="D142" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="F142" s="2">
         <v>8754425672</v>
       </c>
       <c r="G142" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="H142" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="H142" s="10" t="s">
+      <c r="I142" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="I142" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J142" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B143" s="2" t="s">
+      <c r="C143" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="D143" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="F143" s="2">
         <v>7397271607</v>
       </c>
       <c r="G143" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>722</v>
       </c>
-      <c r="H143" s="10" t="s">
+      <c r="I143" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="I143" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J143" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B144" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="D144" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="F144" s="2">
         <v>9940085134</v>
       </c>
       <c r="G144" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="H144" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="H144" s="10" t="s">
+      <c r="I144" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="I144" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J144" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="F145" s="2">
         <v>9528537800</v>
       </c>
       <c r="G145" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="H145" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="H145" s="10" t="s">
+      <c r="I145" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="I145" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J145" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B146" s="2" t="s">
+      <c r="C146" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="D146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="F146" s="2">
         <v>8438234525</v>
       </c>
       <c r="G146" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="H146" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="H146" s="10" t="s">
+      <c r="I146" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="I146" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J146" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="D147" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="F147" s="2">
         <v>9566029509</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="H147" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="H147" s="10" t="s">
+      <c r="I147" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="I147" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J147" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="D148" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="F148" s="2">
         <v>9941014154</v>
       </c>
       <c r="G148" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="H148" s="10" t="s">
         <v>747</v>
-      </c>
-      <c r="H148" s="10" t="s">
-        <v>748</v>
       </c>
       <c r="I148" s="10" t="s">
         <v>17</v>
@@ -7684,28 +7682,28 @@
     </row>
     <row r="149" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="D149" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="F149" s="2">
         <v>9176404337</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="H149" s="10" t="s">
         <v>752</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>753</v>
       </c>
       <c r="I149" s="10" t="s">
         <v>29</v>
@@ -7714,254 +7712,254 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="D150" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="F150" s="2">
         <v>7780198696</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="H150" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="H150" s="10" t="s">
+      <c r="I150" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="I150" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J150" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="F151" s="2">
         <v>9094741005</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="H151" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="H151" s="10" t="s">
+      <c r="I151" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="I151" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J151" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B152" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="F152" s="2">
         <v>9884020052</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="H152" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="H152" s="10" t="s">
+      <c r="I152" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="I152" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J152" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F153" s="2">
         <v>8148182630</v>
       </c>
       <c r="G153" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="H153" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="H153" s="10" t="s">
+      <c r="I153" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J153" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="I153" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J153" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F154" s="2">
         <v>7871171706</v>
       </c>
       <c r="G154" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="H154" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="H154" s="10" t="s">
+      <c r="I154" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="I154" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F155" s="2">
         <v>8754412114</v>
       </c>
       <c r="G155" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="H155" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="H155" s="10" t="s">
+      <c r="I155" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J155" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="I155" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J155" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B156" s="2" t="s">
+      <c r="C156" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F156" s="2">
         <v>9677025777</v>
       </c>
       <c r="G156" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="H156" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="H156" s="10" t="s">
+      <c r="I156" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I156" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J156" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B157" s="2" t="s">
+      <c r="C157" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F157" s="2">
         <v>9486326998</v>
       </c>
       <c r="G157" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>792</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>793</v>
       </c>
       <c r="I157" s="10" t="s">
         <v>17</v>
@@ -7972,28 +7970,28 @@
     </row>
     <row r="158" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F158" s="2">
         <v>9790931473</v>
       </c>
       <c r="G158" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="H158" s="10" t="s">
         <v>797</v>
-      </c>
-      <c r="H158" s="10" t="s">
-        <v>798</v>
       </c>
       <c r="I158" s="10" t="s">
         <v>29</v>
@@ -8004,28 +8002,28 @@
     </row>
     <row r="159" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="D159" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="F159" s="2">
         <v>9962573944</v>
       </c>
       <c r="G159" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>802</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>803</v>
       </c>
       <c r="I159" s="10" t="s">
         <v>29</v>
@@ -8036,28 +8034,28 @@
     </row>
     <row r="160" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="D160" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>806</v>
       </c>
       <c r="F160" s="2">
         <v>9307444445</v>
       </c>
       <c r="G160" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="H160" s="10" t="s">
         <v>807</v>
-      </c>
-      <c r="H160" s="10" t="s">
-        <v>808</v>
       </c>
       <c r="I160" s="10" t="s">
         <v>29</v>
@@ -8066,31 +8064,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="D161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>811</v>
       </c>
       <c r="F161" s="2">
         <v>8667742498</v>
       </c>
       <c r="G161" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="H161" s="10" t="s">
         <v>812</v>
       </c>
-      <c r="H161" s="10" t="s">
-        <v>813</v>
-      </c>
       <c r="I161" s="10" t="s">
         <v>17</v>
       </c>
@@ -8099,6 +8097,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J161" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="Not Logged In"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D42:D55 D57:D59 D61 D122:D156 E157:E161" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Male,Female"</formula1>

--- a/Walkathon Nominations 2026_Final.xlsx
+++ b/Walkathon Nominations 2026_Final.xlsx
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">

--- a/Walkathon Nominations 2026_Final.xlsx
+++ b/Walkathon Nominations 2026_Final.xlsx
@@ -3780,7 +3780,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="J160" s="10" t="inlineStr">
         <is>
-          <t>Not Logged In</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
